--- a/Bitacora_8.xlsx
+++ b/Bitacora_8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgpactual-my.sharepoint.com/personal/juan_alcala_btgpactual_com/Documents/Bitacoras/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgpactual-my.sharepoint.com/personal/juan_alcala_btgpactual_com/Documents/Escritorio/Bitacoras/bitacoras/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="351" documentId="8_{B11B8281-ACE1-4350-8618-021BE984FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC8AB5E-A6F7-40C9-BBDB-705E52C2CF41}"/>
+  <xr:revisionPtr revIDLastSave="485" documentId="8_{B11B8281-ACE1-4350-8618-021BE984FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A46F59-0177-4A01-826C-0643A79795A8}"/>
   <bookViews>
-    <workbookView xWindow="-4005" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="235">
   <si>
     <t>Código: 
 GFPI-F-147</t>
@@ -508,9 +508,6 @@
     <t>BTG Pactual</t>
   </si>
   <si>
-    <t xml:space="preserve">Desde 01/01/2026  hasta 15/01/2025 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Santiago Pulgarin Vazquez </t>
   </si>
   <si>
@@ -676,66 +673,6 @@
     <t xml:space="preserve">Y/O COMENTARIOS  REALIZADOS POR LAS PERSONAS CON ROL DE: APRENDIZ Y/O JEFE INMEDIATO </t>
   </si>
   <si>
-    <t xml:space="preserve">Realice de forma local la solucion de mi HU de forma local </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esto ayudo a que el codigo despues de que pasara por otra revision </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desplegue la solucion de mi HU hacia DEV (Ambiente de pruebas)  para poder probar </t>
-  </si>
-  <si>
-    <t>Pagina de DEV privada de Dominus</t>
-  </si>
-  <si>
-    <t>Se realizaron prubas graficas de este HU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genere documentacion de esta HU  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">En CONFLUENCE pagina privada de la empresa se genro documentacion para guiar las proxima personas que tenga el mismo HU </t>
-  </si>
-  <si>
-    <t>Intrucciones creadas para las proximas personas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realice cambios en la DynamoBD  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realice cambios en la DynamoDB para que los ajuste que realice se pueda seguir ejecutando a nivel de front </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cambios realizados en la dynamoc de aws </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mis compañeros me dieron feedback sobre la implemnetacion del codigo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subi un PR en azure y mis compañeros me hicieron comentarios de mejora </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se me asigno un HT nuevo para traer datos de una tabla </t>
-  </si>
-  <si>
-    <t xml:space="preserve">En una reunion se me asigno un caso nuevo </t>
-  </si>
-  <si>
-    <t>Implemente la solcion del habilitador tecnico a nivel local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En la copia del repositorio del proyecto a nivel local </t>
-  </si>
-  <si>
-    <t>Realice el codigo a nivel local para traer los datos de la base de datos</t>
-  </si>
-  <si>
-    <t>Subi de forma oficial el servicio a DEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subi los cambios que tenia a nivel local con un PR a el repo en la nube </t>
-  </si>
-  <si>
     <t xml:space="preserve">Decreto 055 de 2015, por el cual se reglamenta la afiliación de estudiantes al Sistema General de Riesgos Laborales y se dictan otras disposiciones </t>
   </si>
   <si>
@@ -907,12 +844,111 @@
   <si>
     <t>firma el instructor que recibe la bitácora</t>
   </si>
+  <si>
+    <t xml:space="preserve">Desde 15/01/2026  hasta 30/01/2026 </t>
+  </si>
+  <si>
+    <t>Cambié los tipos de request y service para el accounts-omnibus handler</t>
+  </si>
+  <si>
+    <t>Corregí los code smells en la sección data provider de todos los servicios</t>
+  </si>
+  <si>
+    <t>Corregí las constantes de nombres de archivo para HOLDERS en allowed-file-names y query</t>
+  </si>
+  <si>
+    <t>Actualicé el valor por defecto de uploadDate usando moment-timezone</t>
+  </si>
+  <si>
+    <t>Implementé las soluciones a los comentarios realizados en el PR</t>
+  </si>
+  <si>
+    <t>Corregí el espaciado y la tabulación en los docstrings</t>
+  </si>
+  <si>
+    <t>Cambié el nombre del entorno de operaciones manuales</t>
+  </si>
+  <si>
+    <t>Modifiqué las pruebas unitarias del manual operations handler</t>
+  </si>
+  <si>
+    <t>Implementé un enabler en el código front-end para que HT funcionara en Dominus</t>
+  </si>
+  <si>
+    <t>Modifiqué la consulta de portafolio para permitir validaciones de título en orden</t>
+  </si>
+  <si>
+    <t>Creé la función para formatear la cuenta de inversionista</t>
+  </si>
+  <si>
+    <t>Los ajustes fueron confirmados y cargados en el repositorio de Azure</t>
+  </si>
+  <si>
+    <t>SonarQube validó la corrección de los code smells y los cambios quedaron registrados en Azure</t>
+  </si>
+  <si>
+    <t>Los cambios se integraron en el repositorio de Azure</t>
+  </si>
+  <si>
+    <t>La modificación fue subida al repositorio y validada en Azure</t>
+  </si>
+  <si>
+    <t>El PR fue actualizado y los cambios quedaron almacenados en Azure</t>
+  </si>
+  <si>
+    <t>La documentación ajustada se subió al repositorio en Azure</t>
+  </si>
+  <si>
+    <t>La configuración fue modificada y registrada en Azure</t>
+  </si>
+  <si>
+    <t>Las pruebas corregidas se subieron al repositorio en Azure</t>
+  </si>
+  <si>
+    <t>La nueva funcionalidad quedó disponible en el repositorio de Azure</t>
+  </si>
+  <si>
+    <t>La query ajustada fue subida y validada en Azure</t>
+  </si>
+  <si>
+    <t>La nueva función quedó implementada y registrada en Azure</t>
+  </si>
+  <si>
+    <t>No se presentaron dificultades</t>
+  </si>
+  <si>
+    <t>Mejoré la mantenibilidad del código</t>
+  </si>
+  <si>
+    <t>Fueron cambios menores</t>
+  </si>
+  <si>
+    <t>Validación realizada con éxito</t>
+  </si>
+  <si>
+    <t>Atendí el feedback recibido</t>
+  </si>
+  <si>
+    <t>Mejoré la legibilidad</t>
+  </si>
+  <si>
+    <t>Fue un ajuste menor</t>
+  </si>
+  <si>
+    <t>Validación completada</t>
+  </si>
+  <si>
+    <t>Integración realizada con éxito</t>
+  </si>
+  <si>
+    <t>Añadí validaciones necesarias</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1223,7 +1259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="89">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -1402,19 +1438,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1974,45 +1997,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -2323,12 +2311,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="291">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2439,16 +2453,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2457,34 +2471,34 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2499,703 +2513,691 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="79" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="48" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="83" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="74" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="52" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="71" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="53" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3743,13 +3745,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1756833</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>179917</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1629834</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>137582</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3793,13 +3795,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1076325</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4206,7 +4208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H59"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="2" width="47.42578125" style="58" customWidth="1"/>
@@ -4216,7 +4218,7 @@
     <col min="7" max="7" width="46.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="28.5" customHeight="1">
+    <row r="1" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="67"/>
       <c r="C1" s="68"/>
       <c r="D1" s="68"/>
@@ -4227,7 +4229,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="2:8" ht="28.5" customHeight="1">
+    <row r="2" spans="2:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="70"/>
       <c r="C2" s="54"/>
       <c r="D2" s="54"/>
@@ -4238,582 +4240,582 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="2:8" ht="25.5" customHeight="1">
-      <c r="B3" s="196" t="s">
+    <row r="3" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="198"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="176"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="2:8" ht="25.5" customHeight="1">
-      <c r="B4" s="199" t="s">
+    <row r="4" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="179"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="2:8" ht="25.5" customHeight="1">
-      <c r="B5" s="202" t="s">
+    <row r="5" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="203"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="204"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="182"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="2:8" ht="25.5" customHeight="1">
-      <c r="B6" s="199" t="s">
+    <row r="6" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="200"/>
-      <c r="D6" s="200"/>
-      <c r="E6" s="201"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="179"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="2:8" ht="25.5" customHeight="1">
-      <c r="B7" s="196" t="s">
+    <row r="7" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="197"/>
-      <c r="D7" s="197"/>
-      <c r="E7" s="198"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="176"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="2:8" ht="31.5" customHeight="1">
+    <row r="8" spans="2:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="72" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="205" t="s">
+      <c r="D8" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="206"/>
+      <c r="E8" s="184"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="2:8" ht="25.5" customHeight="1">
-      <c r="B9" s="207" t="s">
+    <row r="9" spans="2:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="209"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="186"/>
+      <c r="E9" s="187"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="2:8" ht="17.25" customHeight="1">
-      <c r="B10" s="210" t="s">
+    <row r="10" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="211"/>
-      <c r="D10" s="211"/>
-      <c r="E10" s="212"/>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="188" t="s">
+      <c r="C10" s="189"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="190"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="189"/>
-      <c r="D11" s="189"/>
-      <c r="E11" s="190"/>
-    </row>
-    <row r="12" spans="2:8" ht="51" customHeight="1">
-      <c r="B12" s="179" t="s">
+      <c r="C11" s="192"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="193"/>
+    </row>
+    <row r="12" spans="2:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="180"/>
-      <c r="D12" s="181"/>
-      <c r="E12" s="182"/>
+      <c r="C12" s="171"/>
+      <c r="D12" s="172"/>
+      <c r="E12" s="173"/>
       <c r="F12" s="1"/>
       <c r="G12" s="36"/>
     </row>
-    <row r="13" spans="2:8" ht="12.75" customHeight="1">
+    <row r="13" spans="2:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="78"/>
       <c r="C13" s="79"/>
       <c r="D13" s="79"/>
       <c r="E13" s="80"/>
     </row>
-    <row r="14" spans="2:8" ht="27.75" customHeight="1">
-      <c r="B14" s="170" t="s">
+    <row r="14" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="203" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="172"/>
-    </row>
-    <row r="15" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B15" s="173" t="s">
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="205"/>
+    </row>
+    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="206" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="174"/>
-      <c r="D15" s="174"/>
-      <c r="E15" s="175"/>
-    </row>
-    <row r="16" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B16" s="173" t="s">
+      <c r="C15" s="207"/>
+      <c r="D15" s="207"/>
+      <c r="E15" s="208"/>
+    </row>
+    <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="174"/>
-      <c r="D16" s="174"/>
-      <c r="E16" s="175"/>
-    </row>
-    <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="183" t="s">
+      <c r="C16" s="207"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="208"/>
+    </row>
+    <row r="17" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="212" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="184"/>
-      <c r="D17" s="184"/>
-      <c r="E17" s="185"/>
-    </row>
-    <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="173" t="s">
+      <c r="C17" s="213"/>
+      <c r="D17" s="213"/>
+      <c r="E17" s="214"/>
+    </row>
+    <row r="18" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="206" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="174"/>
-      <c r="D18" s="174"/>
-      <c r="E18" s="175"/>
-    </row>
-    <row r="19" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B19" s="173" t="s">
+      <c r="C18" s="207"/>
+      <c r="D18" s="207"/>
+      <c r="E18" s="208"/>
+    </row>
+    <row r="19" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="174"/>
-      <c r="D19" s="174"/>
-      <c r="E19" s="175"/>
-    </row>
-    <row r="20" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B20" s="176" t="s">
+      <c r="C19" s="207"/>
+      <c r="D19" s="207"/>
+      <c r="E19" s="208"/>
+    </row>
+    <row r="20" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="209" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="177"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="178"/>
-    </row>
-    <row r="21" spans="2:6" ht="27" customHeight="1">
-      <c r="B21" s="179" t="s">
+      <c r="C20" s="210"/>
+      <c r="D20" s="210"/>
+      <c r="E20" s="211"/>
+    </row>
+    <row r="21" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="180"/>
-      <c r="D21" s="181"/>
-      <c r="E21" s="182"/>
-    </row>
-    <row r="22" spans="2:6" ht="15" customHeight="1">
-      <c r="B22" s="188" t="s">
+      <c r="C21" s="171"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="173"/>
+    </row>
+    <row r="22" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="191" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="189"/>
-      <c r="D22" s="189" t="s">
+      <c r="C22" s="192"/>
+      <c r="D22" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="190"/>
-    </row>
-    <row r="23" spans="2:6" ht="5.25" customHeight="1">
-      <c r="B23" s="191"/>
-      <c r="C23" s="192"/>
-      <c r="D23" s="192"/>
-      <c r="E23" s="193"/>
-    </row>
-    <row r="24" spans="2:6" ht="14.25" customHeight="1">
+      <c r="E22" s="193"/>
+    </row>
+    <row r="23" spans="2:6" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="194"/>
+      <c r="C23" s="195"/>
+      <c r="D23" s="195"/>
+      <c r="E23" s="196"/>
+    </row>
+    <row r="24" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="194" t="s">
+      <c r="D24" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="195"/>
+      <c r="E24" s="198"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="74" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="186"/>
-      <c r="E25" s="187"/>
-    </row>
-    <row r="26" spans="2:6" ht="31.5">
+      <c r="D25" s="199"/>
+      <c r="E25" s="200"/>
+    </row>
+    <row r="26" spans="2:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B26" s="62" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="186"/>
-      <c r="E26" s="187"/>
-    </row>
-    <row r="27" spans="2:6" ht="45">
+      <c r="D26" s="199"/>
+      <c r="E26" s="200"/>
+    </row>
+    <row r="27" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B27" s="64" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="186"/>
-      <c r="E27" s="187"/>
-    </row>
-    <row r="28" spans="2:6" ht="21" customHeight="1">
+      <c r="D27" s="199"/>
+      <c r="E27" s="200"/>
+    </row>
+    <row r="28" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="74" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="186"/>
-      <c r="E28" s="187"/>
-    </row>
-    <row r="29" spans="2:6" ht="44.25" customHeight="1">
+      <c r="D28" s="199"/>
+      <c r="E28" s="200"/>
+    </row>
+    <row r="29" spans="2:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="74" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="186" t="s">
+      <c r="D29" s="199" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="187" t="s">
+      <c r="E29" s="200" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="36.75" customHeight="1">
+    <row r="30" spans="2:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="74" t="s">
         <v>37</v>
       </c>
       <c r="C30" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="186" t="s">
+      <c r="D30" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="187" t="s">
+      <c r="E30" s="200" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="30">
+    <row r="31" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="74" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="186"/>
-      <c r="E31" s="187"/>
-    </row>
-    <row r="32" spans="2:6" ht="65.25" customHeight="1">
+      <c r="D31" s="199"/>
+      <c r="E31" s="200"/>
+    </row>
+    <row r="32" spans="2:6" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="74" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="186" t="s">
+      <c r="D32" s="199" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="187" t="s">
+      <c r="E32" s="200" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="2:5" ht="75">
+    <row r="33" spans="2:5" ht="75" x14ac:dyDescent="0.25">
       <c r="B33" s="74" t="s">
         <v>45</v>
       </c>
       <c r="C33" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="186"/>
-      <c r="E33" s="187"/>
-    </row>
-    <row r="34" spans="2:5" ht="60">
+      <c r="D33" s="199"/>
+      <c r="E33" s="200"/>
+    </row>
+    <row r="34" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B34" s="74" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="186"/>
-      <c r="E34" s="187"/>
-    </row>
-    <row r="35" spans="2:5" ht="60">
+      <c r="D34" s="199"/>
+      <c r="E34" s="200"/>
+    </row>
+    <row r="35" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B35" s="74" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="186"/>
-      <c r="E35" s="187"/>
-    </row>
-    <row r="36" spans="2:5" ht="45">
+      <c r="D35" s="199"/>
+      <c r="E35" s="200"/>
+    </row>
+    <row r="36" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B36" s="74" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="186"/>
-      <c r="E36" s="187"/>
-    </row>
-    <row r="37" spans="2:5" ht="60">
+      <c r="D36" s="199"/>
+      <c r="E36" s="200"/>
+    </row>
+    <row r="37" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B37" s="74" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="186"/>
-      <c r="E37" s="187"/>
-    </row>
-    <row r="38" spans="2:5" ht="60">
+      <c r="D37" s="199"/>
+      <c r="E37" s="200"/>
+    </row>
+    <row r="38" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B38" s="74" t="s">
         <v>55</v>
       </c>
       <c r="C38" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="186"/>
-      <c r="E38" s="187"/>
-    </row>
-    <row r="39" spans="2:5" ht="60">
+      <c r="D38" s="199"/>
+      <c r="E38" s="200"/>
+    </row>
+    <row r="39" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B39" s="74" t="s">
         <v>32</v>
       </c>
       <c r="C39" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="186"/>
-      <c r="E39" s="187"/>
-    </row>
-    <row r="40" spans="2:5" ht="60">
+      <c r="D39" s="199"/>
+      <c r="E39" s="200"/>
+    </row>
+    <row r="40" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B40" s="74" t="s">
         <v>58</v>
       </c>
       <c r="C40" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="186"/>
-      <c r="E40" s="187"/>
-    </row>
-    <row r="41" spans="2:5" ht="60">
+      <c r="D40" s="199"/>
+      <c r="E40" s="200"/>
+    </row>
+    <row r="41" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B41" s="74" t="s">
         <v>60</v>
       </c>
       <c r="C41" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="186"/>
-      <c r="E41" s="187"/>
-    </row>
-    <row r="42" spans="2:5" ht="60">
+      <c r="D41" s="199"/>
+      <c r="E41" s="200"/>
+    </row>
+    <row r="42" spans="2:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B42" s="74" t="s">
         <v>58</v>
       </c>
       <c r="C42" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="186"/>
-      <c r="E42" s="187"/>
-    </row>
-    <row r="43" spans="2:5" ht="409.5">
+      <c r="D42" s="199"/>
+      <c r="E42" s="200"/>
+    </row>
+    <row r="43" spans="2:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B43" s="74" t="s">
         <v>63</v>
       </c>
       <c r="C43" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="186" t="s">
+      <c r="D43" s="199" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="187" t="s">
+      <c r="E43" s="200" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="2:5" ht="30">
+    <row r="44" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B44" s="74" t="s">
         <v>66</v>
       </c>
       <c r="C44" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="186"/>
-      <c r="E44" s="187"/>
-    </row>
-    <row r="45" spans="2:5" ht="30">
+      <c r="D44" s="199"/>
+      <c r="E44" s="200"/>
+    </row>
+    <row r="45" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="74" t="s">
         <v>68</v>
       </c>
       <c r="C45" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="186"/>
-      <c r="E45" s="187"/>
-    </row>
-    <row r="46" spans="2:5" ht="30">
+      <c r="D45" s="199"/>
+      <c r="E45" s="200"/>
+    </row>
+    <row r="46" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B46" s="74" t="s">
         <v>70</v>
       </c>
       <c r="C46" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="186"/>
-      <c r="E46" s="187"/>
-    </row>
-    <row r="47" spans="2:5" ht="127.5" customHeight="1">
+      <c r="D46" s="199"/>
+      <c r="E46" s="200"/>
+    </row>
+    <row r="47" spans="2:5" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="74" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="186" t="s">
+      <c r="D47" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="187" t="s">
+      <c r="E47" s="200" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:5" ht="45">
+    <row r="48" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" s="74" t="s">
         <v>75</v>
       </c>
       <c r="C48" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="186"/>
-      <c r="E48" s="187"/>
-    </row>
-    <row r="49" spans="2:5" ht="146.25" customHeight="1">
+      <c r="D48" s="199"/>
+      <c r="E48" s="200"/>
+    </row>
+    <row r="49" spans="2:5" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="74" t="s">
         <v>77</v>
       </c>
       <c r="C49" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="186" t="s">
+      <c r="D49" s="199" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="187" t="s">
+      <c r="E49" s="200" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="2:5" ht="339.75" customHeight="1">
+    <row r="50" spans="2:5" ht="339.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="74" t="s">
         <v>80</v>
       </c>
       <c r="C50" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="186" t="s">
+      <c r="D50" s="199" t="s">
         <v>82</v>
       </c>
-      <c r="E50" s="187" t="s">
+      <c r="E50" s="200" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="2:5" ht="84.75" customHeight="1">
+    <row r="51" spans="2:5" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="74" t="s">
         <v>84</v>
       </c>
       <c r="C51" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="186" t="s">
+      <c r="D51" s="199" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="187" t="s">
+      <c r="E51" s="200" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="2:5" ht="90">
+    <row r="52" spans="2:5" ht="90" x14ac:dyDescent="0.25">
       <c r="B52" s="74" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="D52" s="186"/>
-      <c r="E52" s="187"/>
-    </row>
-    <row r="53" spans="2:5" ht="75">
+      <c r="D52" s="199"/>
+      <c r="E52" s="200"/>
+    </row>
+    <row r="53" spans="2:5" ht="75" x14ac:dyDescent="0.25">
       <c r="B53" s="74" t="s">
         <v>89</v>
       </c>
       <c r="C53" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="186"/>
-      <c r="E53" s="187"/>
-    </row>
-    <row r="54" spans="2:5" ht="45">
+      <c r="D53" s="199"/>
+      <c r="E53" s="200"/>
+    </row>
+    <row r="54" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B54" s="74" t="s">
         <v>91</v>
       </c>
       <c r="C54" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="186"/>
-      <c r="E54" s="187"/>
-    </row>
-    <row r="55" spans="2:5" ht="75">
+      <c r="D54" s="199"/>
+      <c r="E54" s="200"/>
+    </row>
+    <row r="55" spans="2:5" ht="75" x14ac:dyDescent="0.25">
       <c r="B55" s="74" t="s">
         <v>93</v>
       </c>
       <c r="C55" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="186"/>
-      <c r="E55" s="187"/>
-    </row>
-    <row r="56" spans="2:5" ht="75">
+      <c r="D55" s="199"/>
+      <c r="E55" s="200"/>
+    </row>
+    <row r="56" spans="2:5" ht="75" x14ac:dyDescent="0.25">
       <c r="B56" s="75" t="s">
         <v>95</v>
       </c>
       <c r="C56" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="186"/>
-      <c r="E56" s="187"/>
-    </row>
-    <row r="57" spans="2:5" ht="37.5" customHeight="1" thickBot="1">
+      <c r="D56" s="199"/>
+      <c r="E56" s="200"/>
+    </row>
+    <row r="57" spans="2:5" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="76" t="s">
         <v>96</v>
       </c>
       <c r="C57" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="168" t="s">
+      <c r="D57" s="201" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="169" t="s">
+      <c r="E57" s="202" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="55"/>
       <c r="C58" s="55"/>
       <c r="D58" s="56"/>
       <c r="E58" s="56"/>
     </row>
-    <row r="59" spans="2:5">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="57"/>
       <c r="C59" s="57"/>
       <c r="D59" s="56"/>
@@ -4821,44 +4823,6 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B19:E19"/>
@@ -4875,6 +4839,44 @@
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4887,8 +4889,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74A078B-FDD5-4F89-B4CB-7471575D0D0F}">
-  <dimension ref="B1:Z84"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="B1:Z87"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="9" customWidth="1"/>
     <col min="2" max="7" width="32.7109375" style="11" customWidth="1"/>
@@ -4908,13 +4910,13 @@
     <col min="27" max="16384" width="11.42578125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" ht="29.25" customHeight="1">
-      <c r="B1" s="125"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="153" t="s">
+    <row r="1" spans="2:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="120"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="10"/>
@@ -4937,13 +4939,13 @@
       <c r="Y1" s="9"/>
       <c r="Z1" s="9"/>
     </row>
-    <row r="2" spans="2:26" ht="29.25" customHeight="1">
-      <c r="B2" s="154"/>
+    <row r="2" spans="2:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="149"/>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="150" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="10"/>
@@ -4966,15 +4968,15 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="2:26" ht="24" customHeight="1">
-      <c r="B3" s="196" t="s">
+    <row r="3" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="198"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="176"/>
       <c r="H3" s="10"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -4995,15 +4997,15 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="2:26" ht="24" customHeight="1">
-      <c r="B4" s="199" t="s">
+    <row r="4" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="201"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="179"/>
       <c r="H4" s="10"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -5024,15 +5026,15 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="2:26" ht="24" customHeight="1">
-      <c r="B5" s="196" t="s">
+    <row r="5" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="174" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="197"/>
-      <c r="G5" s="198"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="176"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
       <c r="J5" s="9"/>
@@ -5053,15 +5055,15 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="2:26" ht="24" customHeight="1">
-      <c r="B6" s="199" t="s">
+    <row r="6" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="200"/>
-      <c r="D6" s="200"/>
-      <c r="E6" s="200"/>
-      <c r="F6" s="200"/>
-      <c r="G6" s="201"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="179"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="9"/>
@@ -5082,15 +5084,15 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="2:26" ht="24" customHeight="1">
-      <c r="B7" s="196" t="s">
+    <row r="7" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="197"/>
-      <c r="D7" s="197"/>
-      <c r="E7" s="197"/>
-      <c r="F7" s="197"/>
-      <c r="G7" s="198"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="175"/>
+      <c r="F7" s="175"/>
+      <c r="G7" s="176"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -5111,19 +5113,19 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="2:26" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B8" s="156" t="s">
+    <row r="8" spans="2:26" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="158" t="s">
+      <c r="C8" s="152"/>
+      <c r="D8" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="157"/>
-      <c r="F8" s="158" t="s">
+      <c r="E8" s="152"/>
+      <c r="F8" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="159"/>
+      <c r="G8" s="154"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -5144,7 +5146,7 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="2:26" ht="9" customHeight="1" thickBot="1">
+    <row r="9" spans="2:26" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="18"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -5171,43 +5173,43 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="2:26" s="11" customFormat="1" ht="29.25" customHeight="1">
-      <c r="B10" s="125" t="s">
+    <row r="10" spans="2:26" s="11" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="137" t="s">
+      <c r="C10" s="132" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="138" t="s">
+      <c r="D10" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="139" t="s">
+      <c r="E10" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="140" t="s">
+      <c r="F10" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="141" t="s">
+      <c r="G10" s="136" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:26" ht="18" customHeight="1" thickBot="1">
-      <c r="B11" s="120" t="s">
+    <row r="11" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="115" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="137" t="s">
         <v>103</v>
       </c>
       <c r="D11" s="89">
         <v>1045423314</v>
       </c>
-      <c r="E11" s="143">
+      <c r="E11" s="138">
         <v>314539922</v>
       </c>
-      <c r="F11" s="162" t="s">
+      <c r="F11" s="157" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="163" t="s">
+      <c r="G11" s="158" t="s">
         <v>105</v>
       </c>
       <c r="H11" s="9"/>
@@ -5230,7 +5232,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="2:26" ht="9" customHeight="1" thickBot="1">
+    <row r="12" spans="2:26" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="18"/>
@@ -5256,17 +5258,17 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="2:26" ht="18" customHeight="1">
-      <c r="B13" s="135" t="s">
+    <row r="13" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="136" t="s">
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="123"/>
-      <c r="G13" s="124"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="119"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
@@ -5285,17 +5287,17 @@
       <c r="X13" s="18"/>
       <c r="Y13" s="18"/>
     </row>
-    <row r="14" spans="2:26" ht="18" customHeight="1" thickBot="1">
-      <c r="B14" s="240">
+    <row r="14" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="219">
         <v>2901692</v>
       </c>
-      <c r="C14" s="241"/>
-      <c r="D14" s="230"/>
-      <c r="E14" s="242" t="s">
+      <c r="C14" s="220"/>
+      <c r="D14" s="221"/>
+      <c r="E14" s="222" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="243"/>
-      <c r="G14" s="244"/>
+      <c r="F14" s="218"/>
+      <c r="G14" s="223"/>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
@@ -5314,7 +5316,7 @@
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
     </row>
-    <row r="15" spans="2:26" ht="9.75" customHeight="1" thickBot="1">
+    <row r="15" spans="2:26" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -5340,21 +5342,21 @@
       <c r="X15" s="15"/>
       <c r="Y15" s="15"/>
     </row>
-    <row r="16" spans="2:26" s="11" customFormat="1" ht="50.25" customHeight="1">
-      <c r="B16" s="125" t="s">
+    <row r="16" spans="2:26" s="11" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="120" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="126"/>
-      <c r="D16" s="130" t="s">
+      <c r="C16" s="121"/>
+      <c r="D16" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="127" t="s">
+      <c r="E16" s="122" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="131" t="s">
+      <c r="F16" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="132"/>
+      <c r="G16" s="127"/>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
       <c r="K16" s="18"/>
@@ -5366,21 +5368,21 @@
       <c r="Y16" s="18"/>
       <c r="Z16" s="12"/>
     </row>
-    <row r="17" spans="2:26" ht="18" customHeight="1" thickBot="1">
-      <c r="B17" s="240" t="s">
+    <row r="17" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="219" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="230"/>
-      <c r="D17" s="133">
+      <c r="C17" s="221"/>
+      <c r="D17" s="128">
         <v>901491551</v>
       </c>
-      <c r="E17" s="134">
-        <v>7</v>
-      </c>
-      <c r="F17" s="245" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="246"/>
+      <c r="E17" s="129">
+        <v>8</v>
+      </c>
+      <c r="F17" s="224" t="s">
+        <v>202</v>
+      </c>
+      <c r="G17" s="225"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
       <c r="K17" s="20"/>
@@ -5391,7 +5393,7 @@
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
     </row>
-    <row r="18" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1">
+    <row r="18" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -5417,21 +5419,21 @@
       <c r="X18" s="15"/>
       <c r="Y18" s="15"/>
     </row>
-    <row r="19" spans="2:26" s="11" customFormat="1" ht="45">
-      <c r="B19" s="125" t="s">
+    <row r="19" spans="2:26" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B19" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="126"/>
-      <c r="D19" s="123" t="s">
+      <c r="C19" s="121"/>
+      <c r="D19" s="118" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="127" t="s">
+      <c r="E19" s="122" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="128" t="s">
+      <c r="F19" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="124"/>
+      <c r="G19" s="119"/>
       <c r="H19" s="18"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
@@ -5447,21 +5449,21 @@
       <c r="Y19" s="18"/>
       <c r="Z19" s="12"/>
     </row>
-    <row r="20" spans="2:26" ht="18" customHeight="1">
-      <c r="B20" s="240" t="s">
+    <row r="20" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="219" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="221"/>
+      <c r="D20" s="161" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="230"/>
-      <c r="D20" s="166" t="s">
+      <c r="E20" s="124">
+        <v>3104546105</v>
+      </c>
+      <c r="F20" s="226" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="129">
-        <v>3104546105</v>
-      </c>
-      <c r="F20" s="231" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="232"/>
+      <c r="G20" s="227"/>
       <c r="H20" s="20"/>
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
@@ -5476,7 +5478,7 @@
       <c r="X20" s="20"/>
       <c r="Y20" s="20"/>
     </row>
-    <row r="21" spans="2:26" ht="8.25" customHeight="1" thickBot="1">
+    <row r="21" spans="2:26" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -5502,15 +5504,15 @@
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
     </row>
-    <row r="22" spans="2:26" ht="18" customHeight="1">
-      <c r="B22" s="220" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="221"/>
-      <c r="D22" s="221"/>
-      <c r="E22" s="221"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="222"/>
+    <row r="22" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="234" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="235"/>
+      <c r="D22" s="235"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="236"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
@@ -5531,21 +5533,21 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="2:26" ht="30" customHeight="1" thickBot="1">
-      <c r="B23" s="160" t="s">
+    <row r="23" spans="2:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="155" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="245" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="229" t="s">
+      <c r="D23" s="221"/>
+      <c r="E23" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="230"/>
-      <c r="E23" s="161" t="s">
+      <c r="F23" s="226" t="s">
         <v>118</v>
       </c>
-      <c r="F23" s="231" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="232"/>
+      <c r="G23" s="227"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -5566,7 +5568,7 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1">
+    <row r="24" spans="2:26" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -5592,10 +5594,10 @@
       <c r="X24" s="15"/>
       <c r="Y24" s="15"/>
     </row>
-    <row r="25" spans="2:26" ht="18" customHeight="1" thickBot="1">
+    <row r="25" spans="2:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="38"/>
       <c r="C25" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" s="38"/>
       <c r="E25" s="24"/>
@@ -5620,21 +5622,21 @@
       <c r="X25" s="23"/>
       <c r="Y25" s="23"/>
     </row>
-    <row r="26" spans="2:26" ht="30" customHeight="1" thickBot="1">
-      <c r="B26" s="144" t="s">
+    <row r="26" spans="2:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="139" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="145" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="146"/>
-      <c r="E26" s="147" t="s">
+      <c r="D26" s="141"/>
+      <c r="E26" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="F26" s="145" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" s="145"/>
+      <c r="G26" s="140"/>
       <c r="H26" s="22"/>
       <c r="I26" s="22"/>
       <c r="J26" s="22"/>
@@ -5654,15 +5656,15 @@
       <c r="X26" s="23"/>
       <c r="Y26" s="23"/>
     </row>
-    <row r="27" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1">
+    <row r="27" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="44"/>
       <c r="C27" s="81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="82"/>
       <c r="E27" s="50"/>
       <c r="F27" s="81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G27" s="83"/>
       <c r="H27" s="18"/>
@@ -5682,17 +5684,17 @@
       <c r="V27" s="20"/>
       <c r="Z27" s="14"/>
     </row>
-    <row r="28" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1">
+    <row r="28" spans="2:26" s="13" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="45"/>
       <c r="C28" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D28" s="40"/>
       <c r="E28" s="51"/>
-      <c r="F28" s="223" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="224"/>
+      <c r="F28" s="237" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="239"/>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="20"/>
@@ -5710,17 +5712,17 @@
       <c r="V28" s="20"/>
       <c r="Z28" s="14"/>
     </row>
-    <row r="29" spans="2:26" s="13" customFormat="1" ht="34.5" customHeight="1">
+    <row r="29" spans="2:26" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="46"/>
       <c r="C29" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" s="40"/>
       <c r="E29" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="F29" s="223"/>
-      <c r="G29" s="224"/>
+        <v>127</v>
+      </c>
+      <c r="F29" s="238"/>
+      <c r="G29" s="240"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
       <c r="J29" s="20"/>
@@ -5738,19 +5740,19 @@
       <c r="V29" s="20"/>
       <c r="Z29" s="14"/>
     </row>
-    <row r="30" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1">
-      <c r="B30" s="149" t="s">
+    <row r="30" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="43" t="s">
         <v>129</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>130</v>
       </c>
       <c r="D30" s="40"/>
       <c r="E30" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="F30" s="21" t="s">
         <v>131</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>132</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="18"/>
@@ -5770,15 +5772,15 @@
       <c r="V30" s="20"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1" thickBot="1">
+    <row r="31" spans="2:26" s="13" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="47"/>
       <c r="C31" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="41"/>
       <c r="E31" s="45"/>
       <c r="F31" s="91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G31" s="86"/>
       <c r="H31" s="18"/>
@@ -5801,18 +5803,18 @@
       <c r="Y31" s="15"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="2:26" s="13" customFormat="1" ht="44.25" customHeight="1">
+    <row r="32" spans="2:26" s="13" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="47"/>
       <c r="C32" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="49"/>
       <c r="F32" s="90" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="159" t="s">
         <v>136</v>
-      </c>
-      <c r="G32" s="164" t="s">
-        <v>137</v>
       </c>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -5834,21 +5836,21 @@
       <c r="Y32" s="15"/>
       <c r="Z32" s="14"/>
     </row>
-    <row r="33" spans="2:26" s="13" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
+    <row r="33" spans="2:26" s="13" customFormat="1" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="48"/>
       <c r="C33" s="89" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="145"/>
+      <c r="E33" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="150"/>
-      <c r="E33" s="87" t="s">
+      <c r="F33" s="42" t="s">
         <v>139</v>
-      </c>
-      <c r="F33" s="42" t="s">
-        <v>140</v>
       </c>
       <c r="G33" s="39"/>
       <c r="H33" s="18"/>
-      <c r="I33" s="167"/>
+      <c r="I33" s="162"/>
       <c r="J33" s="19"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
@@ -5867,15 +5869,15 @@
       <c r="Y33" s="15"/>
       <c r="Z33" s="14"/>
     </row>
-    <row r="34" spans="2:26" s="13" customFormat="1" ht="45.6" customHeight="1" thickBot="1">
+    <row r="34" spans="2:26" s="13" customFormat="1" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="49"/>
       <c r="C34" s="90" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="151"/>
+        <v>140</v>
+      </c>
+      <c r="D34" s="146"/>
       <c r="E34" s="53"/>
       <c r="F34" s="85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G34" s="86"/>
       <c r="H34" s="18"/>
@@ -5898,19 +5900,19 @@
       <c r="Y34" s="15"/>
       <c r="Z34" s="14"/>
     </row>
-    <row r="35" spans="2:26" s="13" customFormat="1" ht="31.5" customHeight="1">
+    <row r="35" spans="2:26" s="13" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="42" t="s">
         <v>143</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>144</v>
       </c>
       <c r="D35" s="40"/>
       <c r="E35" s="87" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" s="88" t="s">
         <v>145</v>
-      </c>
-      <c r="F35" s="88" t="s">
-        <v>146</v>
       </c>
       <c r="G35" s="92"/>
       <c r="H35" s="18"/>
@@ -5933,15 +5935,15 @@
       <c r="Y35" s="15"/>
       <c r="Z35" s="14"/>
     </row>
-    <row r="36" spans="2:26" s="13" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
+    <row r="36" spans="2:26" s="13" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="48"/>
       <c r="C36" s="84" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" s="86"/>
+      <c r="E36" s="143"/>
+      <c r="F36" s="85" t="s">
         <v>147</v>
-      </c>
-      <c r="D36" s="86"/>
-      <c r="E36" s="148"/>
-      <c r="F36" s="85" t="s">
-        <v>148</v>
       </c>
       <c r="G36" s="86"/>
       <c r="H36" s="18"/>
@@ -5964,7 +5966,7 @@
       <c r="Y36" s="15"/>
       <c r="Z36" s="14"/>
     </row>
-    <row r="37" spans="2:26" s="13" customFormat="1" ht="9.75" customHeight="1" thickBot="1">
+    <row r="37" spans="2:26" s="13" customFormat="1" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
       <c r="J37" s="19"/>
@@ -5985,24 +5987,24 @@
       <c r="Y37" s="15"/>
       <c r="Z37" s="14"/>
     </row>
-    <row r="38" spans="2:26" ht="68.25" customHeight="1">
+    <row r="38" spans="2:26" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="93" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="94" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="94" t="s">
+      <c r="D38" s="95" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="95" t="s">
+      <c r="E38" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="95" t="s">
+      <c r="F38" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="95" t="s">
+      <c r="G38" s="96" t="s">
         <v>153</v>
-      </c>
-      <c r="G38" s="96" t="s">
-        <v>154</v>
       </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -6023,20 +6025,20 @@
       <c r="X38" s="18"/>
       <c r="Y38" s="18"/>
     </row>
-    <row r="39" spans="2:26" ht="52.5" customHeight="1" thickBot="1">
-      <c r="B39" s="100" t="s">
+    <row r="39" spans="2:26" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="163" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="164" t="s">
         <v>155</v>
       </c>
-      <c r="C39" s="101" t="s">
+      <c r="D39" s="165"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="166" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="97"/>
-      <c r="E39" s="97"/>
-      <c r="F39" s="98" t="s">
+      <c r="G39" s="167" t="s">
         <v>157</v>
-      </c>
-      <c r="G39" s="99" t="s">
-        <v>158</v>
       </c>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
@@ -6057,20 +6059,22 @@
       <c r="X39" s="18"/>
       <c r="Y39" s="18"/>
     </row>
-    <row r="40" spans="2:26" ht="15" customHeight="1">
-      <c r="B40" s="233" t="s">
-        <v>159</v>
-      </c>
-      <c r="C40" s="234"/>
-      <c r="D40" s="237">
-        <v>46024</v>
-      </c>
-      <c r="E40" s="237">
-        <v>46027</v>
-      </c>
-      <c r="F40" s="239"/>
-      <c r="G40" s="247" t="s">
-        <v>160</v>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B40" s="215" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" s="215"/>
+      <c r="D40" s="282">
+        <v>46038</v>
+      </c>
+      <c r="E40" s="283">
+        <v>46038</v>
+      </c>
+      <c r="F40" s="215" t="s">
+        <v>214</v>
+      </c>
+      <c r="G40" s="215" t="s">
+        <v>225</v>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="18"/>
@@ -6091,13 +6095,13 @@
       <c r="X40" s="18"/>
       <c r="Y40" s="18"/>
     </row>
-    <row r="41" spans="2:26" ht="41.25" customHeight="1" thickBot="1">
-      <c r="B41" s="235"/>
-      <c r="C41" s="236"/>
-      <c r="D41" s="238"/>
-      <c r="E41" s="238"/>
-      <c r="F41" s="238"/>
-      <c r="G41" s="248"/>
+    <row r="41" spans="2:26" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="215"/>
+      <c r="C41" s="215"/>
+      <c r="D41" s="215"/>
+      <c r="E41" s="284"/>
+      <c r="F41" s="215"/>
+      <c r="G41" s="215"/>
       <c r="H41" s="20"/>
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
@@ -6117,22 +6121,22 @@
       <c r="X41" s="18"/>
       <c r="Y41" s="18"/>
     </row>
-    <row r="42" spans="2:26" ht="15" customHeight="1">
-      <c r="B42" s="249" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" s="250"/>
-      <c r="D42" s="237">
-        <v>46024</v>
-      </c>
-      <c r="E42" s="237">
-        <v>46027</v>
-      </c>
-      <c r="F42" s="251" t="s">
-        <v>162</v>
-      </c>
-      <c r="G42" s="252" t="s">
-        <v>163</v>
+    <row r="42" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="215" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="215"/>
+      <c r="D42" s="282">
+        <v>46038</v>
+      </c>
+      <c r="E42" s="283">
+        <v>46038</v>
+      </c>
+      <c r="F42" s="215" t="s">
+        <v>215</v>
+      </c>
+      <c r="G42" s="215" t="s">
+        <v>226</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="18"/>
@@ -6153,13 +6157,13 @@
       <c r="X42" s="18"/>
       <c r="Y42" s="18"/>
     </row>
-    <row r="43" spans="2:26" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B43" s="235"/>
-      <c r="C43" s="236"/>
-      <c r="D43" s="238"/>
-      <c r="E43" s="238"/>
-      <c r="F43" s="238"/>
-      <c r="G43" s="248"/>
+    <row r="43" spans="2:26" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="215"/>
+      <c r="C43" s="215"/>
+      <c r="D43" s="215"/>
+      <c r="E43" s="284"/>
+      <c r="F43" s="215"/>
+      <c r="G43" s="215"/>
       <c r="H43" s="20"/>
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
@@ -6179,22 +6183,22 @@
       <c r="X43" s="18"/>
       <c r="Y43" s="18"/>
     </row>
-    <row r="44" spans="2:26">
-      <c r="B44" s="249" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="250"/>
-      <c r="D44" s="237">
-        <v>46024</v>
-      </c>
-      <c r="E44" s="237">
-        <v>46027</v>
-      </c>
-      <c r="F44" s="251" t="s">
-        <v>165</v>
-      </c>
-      <c r="G44" s="252" t="s">
-        <v>166</v>
+    <row r="44" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="215" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" s="215"/>
+      <c r="D44" s="216">
+        <v>46041</v>
+      </c>
+      <c r="E44" s="216">
+        <v>46041</v>
+      </c>
+      <c r="F44" s="215" t="s">
+        <v>216</v>
+      </c>
+      <c r="G44" s="215" t="s">
+        <v>227</v>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="18"/>
@@ -6215,13 +6219,13 @@
       <c r="X44" s="18"/>
       <c r="Y44" s="18"/>
     </row>
-    <row r="45" spans="2:26" ht="51.75" customHeight="1" thickBot="1">
-      <c r="B45" s="235"/>
-      <c r="C45" s="236"/>
-      <c r="D45" s="238"/>
-      <c r="E45" s="238"/>
-      <c r="F45" s="238"/>
-      <c r="G45" s="248"/>
+    <row r="45" spans="2:26" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="215"/>
+      <c r="C45" s="215"/>
+      <c r="D45" s="215"/>
+      <c r="E45" s="215"/>
+      <c r="F45" s="215"/>
+      <c r="G45" s="215"/>
       <c r="H45" s="20"/>
       <c r="I45" s="18"/>
       <c r="J45" s="18"/>
@@ -6241,22 +6245,22 @@
       <c r="X45" s="18"/>
       <c r="Y45" s="18"/>
     </row>
-    <row r="46" spans="2:26" ht="77.25" customHeight="1">
-      <c r="B46" s="249" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="250"/>
-      <c r="D46" s="237">
-        <v>46024</v>
-      </c>
-      <c r="E46" s="237">
-        <v>46027</v>
-      </c>
-      <c r="F46" s="251" t="s">
-        <v>168</v>
-      </c>
-      <c r="G46" s="252" t="s">
-        <v>169</v>
+    <row r="46" spans="2:26" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="215" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="215"/>
+      <c r="D46" s="216">
+        <v>46041</v>
+      </c>
+      <c r="E46" s="216">
+        <v>46041</v>
+      </c>
+      <c r="F46" s="215" t="s">
+        <v>217</v>
+      </c>
+      <c r="G46" s="215" t="s">
+        <v>228</v>
       </c>
       <c r="H46" s="20"/>
       <c r="I46" s="18"/>
@@ -6277,13 +6281,13 @@
       <c r="X46" s="18"/>
       <c r="Y46" s="18"/>
     </row>
-    <row r="47" spans="2:26" ht="52.5" hidden="1" customHeight="1">
-      <c r="B47" s="235"/>
-      <c r="C47" s="236"/>
-      <c r="D47" s="238"/>
-      <c r="E47" s="238"/>
-      <c r="F47" s="238"/>
-      <c r="G47" s="248"/>
+    <row r="47" spans="2:26" ht="52.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="215"/>
+      <c r="C47" s="215"/>
+      <c r="D47" s="215"/>
+      <c r="E47" s="215"/>
+      <c r="F47" s="215"/>
+      <c r="G47" s="215"/>
       <c r="H47" s="20"/>
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
@@ -6303,21 +6307,23 @@
       <c r="X47" s="18"/>
       <c r="Y47" s="18"/>
     </row>
-    <row r="48" spans="2:26" ht="15" customHeight="1">
-      <c r="B48" s="249" t="s">
-        <v>170</v>
-      </c>
-      <c r="C48" s="250"/>
-      <c r="D48" s="253">
-        <v>46027</v>
-      </c>
-      <c r="E48" s="253">
-        <v>46028</v>
-      </c>
-      <c r="F48" s="251" t="s">
-        <v>171</v>
-      </c>
-      <c r="G48" s="252"/>
+    <row r="48" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="215" t="s">
+        <v>207</v>
+      </c>
+      <c r="C48" s="215"/>
+      <c r="D48" s="216">
+        <v>46044</v>
+      </c>
+      <c r="E48" s="216">
+        <v>46044</v>
+      </c>
+      <c r="F48" s="215" t="s">
+        <v>218</v>
+      </c>
+      <c r="G48" s="215" t="s">
+        <v>229</v>
+      </c>
       <c r="H48" s="20"/>
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
@@ -6337,13 +6343,13 @@
       <c r="X48" s="18"/>
       <c r="Y48" s="18"/>
     </row>
-    <row r="49" spans="2:25">
-      <c r="B49" s="235"/>
-      <c r="C49" s="236"/>
-      <c r="D49" s="238"/>
-      <c r="E49" s="238"/>
-      <c r="F49" s="238"/>
-      <c r="G49" s="248"/>
+    <row r="49" spans="2:25" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="215"/>
+      <c r="C49" s="215"/>
+      <c r="D49" s="215"/>
+      <c r="E49" s="215"/>
+      <c r="F49" s="215"/>
+      <c r="G49" s="215"/>
       <c r="H49" s="20"/>
       <c r="I49" s="18"/>
       <c r="J49" s="18"/>
@@ -6363,21 +6369,23 @@
       <c r="X49" s="18"/>
       <c r="Y49" s="18"/>
     </row>
-    <row r="50" spans="2:25">
-      <c r="B50" s="249" t="s">
-        <v>172</v>
-      </c>
-      <c r="C50" s="250"/>
-      <c r="D50" s="253">
-        <v>46027</v>
-      </c>
-      <c r="E50" s="253">
-        <v>46027</v>
-      </c>
-      <c r="F50" s="251" t="s">
-        <v>173</v>
-      </c>
-      <c r="G50" s="252"/>
+    <row r="50" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="215" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" s="215"/>
+      <c r="D50" s="216">
+        <v>46045</v>
+      </c>
+      <c r="E50" s="216">
+        <v>46045</v>
+      </c>
+      <c r="F50" s="215" t="s">
+        <v>219</v>
+      </c>
+      <c r="G50" s="215" t="s">
+        <v>230</v>
+      </c>
       <c r="H50" s="20"/>
       <c r="I50" s="18"/>
       <c r="J50" s="18"/>
@@ -6397,13 +6405,13 @@
       <c r="X50" s="18"/>
       <c r="Y50" s="18"/>
     </row>
-    <row r="51" spans="2:25">
-      <c r="B51" s="254"/>
-      <c r="C51" s="255"/>
-      <c r="D51" s="256"/>
-      <c r="E51" s="256"/>
-      <c r="F51" s="257"/>
-      <c r="G51" s="258"/>
+    <row r="51" spans="2:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="215"/>
+      <c r="C51" s="215"/>
+      <c r="D51" s="215"/>
+      <c r="E51" s="215"/>
+      <c r="F51" s="215"/>
+      <c r="G51" s="215"/>
       <c r="H51" s="20"/>
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
@@ -6423,22 +6431,22 @@
       <c r="X51" s="18"/>
       <c r="Y51" s="18"/>
     </row>
-    <row r="52" spans="2:25">
-      <c r="B52" s="213" t="s">
-        <v>174</v>
-      </c>
-      <c r="C52" s="213"/>
-      <c r="D52" s="259">
-        <v>6</v>
-      </c>
-      <c r="E52" s="259">
-        <v>15</v>
-      </c>
-      <c r="F52" s="213" t="s">
-        <v>175</v>
-      </c>
-      <c r="G52" s="213" t="s">
-        <v>176</v>
+    <row r="52" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="215" t="s">
+        <v>209</v>
+      </c>
+      <c r="C52" s="215"/>
+      <c r="D52" s="216">
+        <v>46050</v>
+      </c>
+      <c r="E52" s="216">
+        <v>46050</v>
+      </c>
+      <c r="F52" s="215" t="s">
+        <v>220</v>
+      </c>
+      <c r="G52" s="215" t="s">
+        <v>231</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="18"/>
@@ -6459,13 +6467,13 @@
       <c r="X52" s="18"/>
       <c r="Y52" s="18"/>
     </row>
-    <row r="53" spans="2:25">
-      <c r="B53" s="213"/>
-      <c r="C53" s="213"/>
-      <c r="D53" s="259"/>
-      <c r="E53" s="259"/>
-      <c r="F53" s="213"/>
-      <c r="G53" s="213"/>
+    <row r="53" spans="2:25" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="215"/>
+      <c r="C53" s="215"/>
+      <c r="D53" s="215"/>
+      <c r="E53" s="215"/>
+      <c r="F53" s="215"/>
+      <c r="G53" s="215"/>
       <c r="H53" s="20"/>
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
@@ -6485,21 +6493,23 @@
       <c r="X53" s="18"/>
       <c r="Y53" s="18"/>
     </row>
-    <row r="54" spans="2:25" ht="15" customHeight="1">
-      <c r="B54" s="213" t="s">
-        <v>177</v>
-      </c>
-      <c r="C54" s="213"/>
-      <c r="D54" s="253">
-        <v>46036</v>
-      </c>
-      <c r="E54" s="253">
-        <v>46037</v>
-      </c>
-      <c r="F54" s="213" t="s">
-        <v>178</v>
-      </c>
-      <c r="G54" s="213"/>
+    <row r="54" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="215" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" s="215"/>
+      <c r="D54" s="216">
+        <v>46050</v>
+      </c>
+      <c r="E54" s="216">
+        <v>46050</v>
+      </c>
+      <c r="F54" s="215" t="s">
+        <v>221</v>
+      </c>
+      <c r="G54" s="215" t="s">
+        <v>232</v>
+      </c>
       <c r="H54" s="20"/>
       <c r="I54" s="18"/>
       <c r="J54" s="18"/>
@@ -6519,13 +6529,13 @@
       <c r="X54" s="18"/>
       <c r="Y54" s="18"/>
     </row>
-    <row r="55" spans="2:25">
-      <c r="B55" s="213"/>
-      <c r="C55" s="213"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="213"/>
-      <c r="G55" s="213"/>
+    <row r="55" spans="2:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="215"/>
+      <c r="C55" s="215"/>
+      <c r="D55" s="215"/>
+      <c r="E55" s="215"/>
+      <c r="F55" s="215"/>
+      <c r="G55" s="215"/>
       <c r="H55" s="20"/>
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
@@ -6545,13 +6555,23 @@
       <c r="X55" s="18"/>
       <c r="Y55" s="18"/>
     </row>
-    <row r="56" spans="2:25" ht="15" customHeight="1">
-      <c r="B56" s="213"/>
-      <c r="C56" s="213"/>
-      <c r="D56" s="253"/>
-      <c r="E56" s="253"/>
-      <c r="F56" s="213"/>
-      <c r="G56" s="213"/>
+    <row r="56" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="215" t="s">
+        <v>211</v>
+      </c>
+      <c r="C56" s="215"/>
+      <c r="D56" s="216">
+        <v>46050</v>
+      </c>
+      <c r="E56" s="216">
+        <v>46050</v>
+      </c>
+      <c r="F56" s="215" t="s">
+        <v>222</v>
+      </c>
+      <c r="G56" s="215" t="s">
+        <v>233</v>
+      </c>
       <c r="H56" s="20"/>
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
@@ -6571,13 +6591,13 @@
       <c r="X56" s="18"/>
       <c r="Y56" s="18"/>
     </row>
-    <row r="57" spans="2:25">
-      <c r="B57" s="213"/>
-      <c r="C57" s="213"/>
-      <c r="D57" s="238"/>
-      <c r="E57" s="238"/>
-      <c r="F57" s="213"/>
-      <c r="G57" s="213"/>
+    <row r="57" spans="2:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="215"/>
+      <c r="C57" s="215"/>
+      <c r="D57" s="215"/>
+      <c r="E57" s="215"/>
+      <c r="F57" s="215"/>
+      <c r="G57" s="215"/>
       <c r="H57" s="20"/>
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
@@ -6597,13 +6617,23 @@
       <c r="X57" s="18"/>
       <c r="Y57" s="18"/>
     </row>
-    <row r="58" spans="2:25" ht="15" customHeight="1">
-      <c r="B58" s="213"/>
-      <c r="C58" s="213"/>
-      <c r="D58" s="253"/>
-      <c r="E58" s="253"/>
-      <c r="F58" s="213"/>
-      <c r="G58" s="213"/>
+    <row r="58" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="215" t="s">
+        <v>212</v>
+      </c>
+      <c r="C58" s="215"/>
+      <c r="D58" s="216">
+        <v>46050</v>
+      </c>
+      <c r="E58" s="216">
+        <v>46050</v>
+      </c>
+      <c r="F58" s="215" t="s">
+        <v>223</v>
+      </c>
+      <c r="G58" s="215" t="s">
+        <v>234</v>
+      </c>
       <c r="H58" s="20"/>
       <c r="I58" s="18"/>
       <c r="J58" s="18"/>
@@ -6623,13 +6653,13 @@
       <c r="X58" s="18"/>
       <c r="Y58" s="18"/>
     </row>
-    <row r="59" spans="2:25">
-      <c r="B59" s="213"/>
-      <c r="C59" s="213"/>
-      <c r="D59" s="238"/>
-      <c r="E59" s="238"/>
-      <c r="F59" s="213"/>
-      <c r="G59" s="213"/>
+    <row r="59" spans="2:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="215"/>
+      <c r="C59" s="215"/>
+      <c r="D59" s="215"/>
+      <c r="E59" s="215"/>
+      <c r="F59" s="215"/>
+      <c r="G59" s="215"/>
       <c r="H59" s="20"/>
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
@@ -6649,13 +6679,23 @@
       <c r="X59" s="18"/>
       <c r="Y59" s="18"/>
     </row>
-    <row r="60" spans="2:25" ht="15" customHeight="1" thickBot="1">
-      <c r="B60" s="27"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
+    <row r="60" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="285" t="s">
+        <v>213</v>
+      </c>
+      <c r="C60" s="286"/>
+      <c r="D60" s="216">
+        <v>46051</v>
+      </c>
+      <c r="E60" s="216">
+        <v>46051</v>
+      </c>
+      <c r="F60" s="289" t="s">
+        <v>224</v>
+      </c>
+      <c r="G60" s="289" t="s">
+        <v>225</v>
+      </c>
       <c r="H60" s="20"/>
       <c r="I60" s="18"/>
       <c r="J60" s="18"/>
@@ -6675,155 +6715,149 @@
       <c r="X60" s="18"/>
       <c r="Y60" s="18"/>
     </row>
-    <row r="61" spans="2:25" ht="23.25" customHeight="1">
-      <c r="B61" s="102"/>
-      <c r="C61" s="103" t="s">
-        <v>179</v>
-      </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="105"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="22"/>
-      <c r="V61" s="22"/>
-      <c r="W61" s="22"/>
-      <c r="X61" s="22"/>
-      <c r="Y61" s="22"/>
-    </row>
-    <row r="62" spans="2:25" ht="19.5" customHeight="1">
-      <c r="B62" s="226" t="s">
-        <v>180</v>
-      </c>
-      <c r="C62" s="227"/>
-      <c r="D62" s="227"/>
-      <c r="E62" s="227"/>
-      <c r="F62" s="227"/>
-      <c r="G62" s="228"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
-      <c r="P62" s="22"/>
-      <c r="Q62" s="22"/>
-      <c r="R62" s="22"/>
-      <c r="S62" s="22"/>
-      <c r="T62" s="22"/>
-      <c r="U62" s="22"/>
-      <c r="V62" s="22"/>
-      <c r="W62" s="22"/>
-      <c r="X62" s="22"/>
-      <c r="Y62" s="22"/>
-    </row>
-    <row r="63" spans="2:25" ht="16.5" customHeight="1">
-      <c r="B63" s="106" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
-      <c r="T63" s="29"/>
-      <c r="U63" s="29"/>
-      <c r="V63" s="29"/>
-      <c r="W63" s="29"/>
-      <c r="X63" s="29"/>
-      <c r="Y63" s="29"/>
-    </row>
-    <row r="64" spans="2:25" ht="16.5" customHeight="1">
-      <c r="B64" s="108" t="s">
-        <v>182</v>
-      </c>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="109"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-    </row>
-    <row r="65" spans="2:26" ht="16.5" customHeight="1">
-      <c r="B65" s="108" t="s">
-        <v>183</v>
-      </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="109"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="29"/>
-      <c r="K65" s="29"/>
-      <c r="L65" s="29"/>
-      <c r="M65" s="29"/>
-      <c r="N65" s="29"/>
-      <c r="O65" s="29"/>
-      <c r="P65" s="29"/>
-      <c r="Q65" s="29"/>
-      <c r="R65" s="29"/>
-      <c r="S65" s="29"/>
-      <c r="T65" s="29"/>
-      <c r="U65" s="29"/>
-      <c r="V65" s="29"/>
-      <c r="W65" s="29"/>
-      <c r="X65" s="29"/>
-      <c r="Y65" s="29"/>
-    </row>
-    <row r="66" spans="2:26" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B66" s="108" t="s">
-        <v>184</v>
-      </c>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="109"/>
+    <row r="61" spans="2:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="287"/>
+      <c r="C61" s="288"/>
+      <c r="D61" s="215"/>
+      <c r="E61" s="215"/>
+      <c r="F61" s="290"/>
+      <c r="G61" s="290"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
+      <c r="R61" s="18"/>
+      <c r="S61" s="18"/>
+      <c r="T61" s="18"/>
+      <c r="U61" s="18"/>
+      <c r="V61" s="18"/>
+      <c r="W61" s="18"/>
+      <c r="X61" s="18"/>
+      <c r="Y61" s="18"/>
+    </row>
+    <row r="62" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B62" s="280"/>
+      <c r="C62" s="281"/>
+      <c r="D62" s="169"/>
+      <c r="E62" s="169"/>
+      <c r="F62" s="168"/>
+      <c r="G62" s="168"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="18"/>
+      <c r="T62" s="18"/>
+      <c r="U62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="W62" s="18"/>
+      <c r="X62" s="18"/>
+      <c r="Y62" s="18"/>
+    </row>
+    <row r="63" spans="2:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="27"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="18"/>
+      <c r="Q63" s="18"/>
+      <c r="R63" s="18"/>
+      <c r="S63" s="18"/>
+      <c r="T63" s="18"/>
+      <c r="U63" s="18"/>
+      <c r="V63" s="18"/>
+      <c r="W63" s="18"/>
+      <c r="X63" s="18"/>
+      <c r="Y63" s="18"/>
+    </row>
+    <row r="64" spans="2:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="97"/>
+      <c r="C64" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="D64" s="99"/>
+      <c r="E64" s="99"/>
+      <c r="F64" s="99"/>
+      <c r="G64" s="100"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
+      <c r="P64" s="22"/>
+      <c r="Q64" s="22"/>
+      <c r="R64" s="22"/>
+      <c r="S64" s="22"/>
+      <c r="T64" s="22"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+      <c r="X64" s="22"/>
+      <c r="Y64" s="22"/>
+    </row>
+    <row r="65" spans="2:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="242" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" s="243"/>
+      <c r="D65" s="243"/>
+      <c r="E65" s="243"/>
+      <c r="F65" s="243"/>
+      <c r="G65" s="244"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="22"/>
+      <c r="P65" s="22"/>
+      <c r="Q65" s="22"/>
+      <c r="R65" s="22"/>
+      <c r="S65" s="22"/>
+      <c r="T65" s="22"/>
+      <c r="U65" s="22"/>
+      <c r="V65" s="22"/>
+      <c r="W65" s="22"/>
+      <c r="X65" s="22"/>
+      <c r="Y65" s="22"/>
+    </row>
+    <row r="66" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="101" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="102"/>
       <c r="H66" s="29"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
@@ -6843,111 +6877,109 @@
       <c r="X66" s="29"/>
       <c r="Y66" s="29"/>
     </row>
-    <row r="67" spans="2:26" ht="79.5" customHeight="1">
-      <c r="B67" s="115" t="s">
+    <row r="67" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="103" t="s">
+        <v>161</v>
+      </c>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="29"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="29"/>
+      <c r="W67" s="29"/>
+      <c r="X67" s="29"/>
+      <c r="Y67" s="29"/>
+    </row>
+    <row r="68" spans="2:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="103" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="29"/>
+      <c r="P68" s="29"/>
+      <c r="Q68" s="29"/>
+      <c r="R68" s="29"/>
+      <c r="S68" s="29"/>
+      <c r="T68" s="29"/>
+      <c r="U68" s="29"/>
+      <c r="V68" s="29"/>
+      <c r="W68" s="29"/>
+      <c r="X68" s="29"/>
+      <c r="Y68" s="29"/>
+    </row>
+    <row r="69" spans="2:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="103" t="s">
+        <v>163</v>
+      </c>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="104"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="29"/>
+      <c r="P69" s="29"/>
+      <c r="Q69" s="29"/>
+      <c r="R69" s="29"/>
+      <c r="S69" s="29"/>
+      <c r="T69" s="29"/>
+      <c r="U69" s="29"/>
+      <c r="V69" s="29"/>
+      <c r="W69" s="29"/>
+      <c r="X69" s="29"/>
+      <c r="Y69" s="29"/>
+    </row>
+    <row r="70" spans="2:26" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="C67" s="116" t="s">
+      <c r="C70" s="111" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="117" t="s">
+      <c r="D70" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="E67" s="118" t="s">
-        <v>185</v>
-      </c>
-      <c r="F67" s="117" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" s="119" t="s">
-        <v>185</v>
-      </c>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="18"/>
-      <c r="P67" s="18"/>
-      <c r="Q67" s="18"/>
-      <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
-      <c r="T67" s="18"/>
-      <c r="U67" s="18"/>
-      <c r="V67" s="18"/>
-      <c r="W67" s="18"/>
-      <c r="X67" s="18"/>
-      <c r="Y67" s="18"/>
-      <c r="Z67" s="18"/>
-    </row>
-    <row r="68" spans="2:26" ht="32.25" customHeight="1" thickBot="1">
-      <c r="B68" s="110" t="s">
-        <v>187</v>
-      </c>
-      <c r="C68" s="111">
-        <v>1</v>
-      </c>
-      <c r="D68" s="112"/>
-      <c r="E68" s="113"/>
-      <c r="F68" s="112"/>
-      <c r="G68" s="114"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="18"/>
-      <c r="P68" s="18"/>
-      <c r="Q68" s="18"/>
-      <c r="R68" s="18"/>
-      <c r="S68" s="18"/>
-      <c r="T68" s="18"/>
-      <c r="U68" s="18"/>
-      <c r="V68" s="18"/>
-      <c r="W68" s="18"/>
-      <c r="X68" s="18"/>
-      <c r="Y68" s="18"/>
-      <c r="Z68" s="18"/>
-    </row>
-    <row r="69" spans="2:26" ht="17.25" customHeight="1">
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-      <c r="N69" s="18"/>
-      <c r="O69" s="18"/>
-      <c r="P69" s="18"/>
-      <c r="Q69" s="18"/>
-      <c r="R69" s="18"/>
-      <c r="S69" s="18"/>
-      <c r="T69" s="18"/>
-      <c r="U69" s="18"/>
-      <c r="V69" s="18"/>
-      <c r="W69" s="18"/>
-      <c r="X69" s="18"/>
-      <c r="Y69" s="18"/>
-      <c r="Z69" s="18"/>
-    </row>
-    <row r="70" spans="2:26" ht="15" customHeight="1">
-      <c r="C70" s="30"/>
-      <c r="D70" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
+      <c r="E70" s="113" t="s">
+        <v>164</v>
+      </c>
+      <c r="F70" s="112" t="s">
+        <v>165</v>
+      </c>
+      <c r="G70" s="114" t="s">
+        <v>164</v>
+      </c>
       <c r="H70" s="18"/>
       <c r="I70" s="18"/>
       <c r="J70" s="18"/>
@@ -6968,13 +7000,17 @@
       <c r="Y70" s="18"/>
       <c r="Z70" s="18"/>
     </row>
-    <row r="71" spans="2:26" ht="15" customHeight="1">
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
+    <row r="71" spans="2:26" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="105" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" s="106">
+        <v>1</v>
+      </c>
+      <c r="D71" s="107"/>
+      <c r="E71" s="108"/>
+      <c r="F71" s="107"/>
+      <c r="G71" s="109"/>
       <c r="H71" s="18"/>
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
@@ -6995,13 +7031,13 @@
       <c r="Y71" s="18"/>
       <c r="Z71" s="18"/>
     </row>
-    <row r="72" spans="2:26" ht="15" customHeight="1">
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
+    <row r="72" spans="2:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
       <c r="H72" s="18"/>
       <c r="I72" s="18"/>
       <c r="J72" s="18"/>
@@ -7022,14 +7058,14 @@
       <c r="Y72" s="18"/>
       <c r="Z72" s="18"/>
     </row>
-    <row r="73" spans="2:26" ht="15" customHeight="1" thickBot="1">
-      <c r="B73" s="260"/>
-      <c r="C73" s="260"/>
-      <c r="D73" s="260"/>
-      <c r="F73" s="165">
-        <v>46021</v>
-      </c>
-      <c r="G73" s="18"/>
+    <row r="73" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="30"/>
+      <c r="D73" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
       <c r="H73" s="18"/>
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
@@ -7050,16 +7086,13 @@
       <c r="Y73" s="18"/>
       <c r="Z73" s="18"/>
     </row>
-    <row r="74" spans="2:26" ht="15" customHeight="1">
-      <c r="B74" s="225" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="225"/>
-      <c r="D74" s="225"/>
-      <c r="F74" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G74" s="18"/>
+    <row r="74" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
       <c r="H74" s="18"/>
       <c r="I74" s="18"/>
       <c r="J74" s="18"/>
@@ -7080,12 +7113,13 @@
       <c r="Y74" s="18"/>
       <c r="Z74" s="18"/>
     </row>
-    <row r="75" spans="2:26">
-      <c r="B75" s="9"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="9"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
+    <row r="75" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
       <c r="H75" s="18"/>
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
@@ -7106,11 +7140,13 @@
       <c r="Y75" s="18"/>
       <c r="Z75" s="18"/>
     </row>
-    <row r="76" spans="2:26" ht="15" customHeight="1">
-      <c r="B76" s="9"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="9"/>
-      <c r="F76" s="20"/>
+    <row r="76" spans="2:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="217"/>
+      <c r="C76" s="217"/>
+      <c r="D76" s="217"/>
+      <c r="F76" s="160">
+        <v>46021</v>
+      </c>
       <c r="G76" s="18"/>
       <c r="H76" s="18"/>
       <c r="I76" s="18"/>
@@ -7132,12 +7168,16 @@
       <c r="Y76" s="18"/>
       <c r="Z76" s="18"/>
     </row>
-    <row r="77" spans="2:26" ht="15" customHeight="1" thickBot="1">
-      <c r="B77" s="260"/>
-      <c r="C77" s="260"/>
-      <c r="D77" s="260"/>
-      <c r="F77" s="243"/>
-      <c r="G77" s="243"/>
+    <row r="77" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="241" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="241"/>
+      <c r="D77" s="241"/>
+      <c r="F77" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G77" s="18"/>
       <c r="H77" s="18"/>
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
@@ -7158,16 +7198,12 @@
       <c r="Y77" s="18"/>
       <c r="Z77" s="18"/>
     </row>
-    <row r="78" spans="2:26" ht="15.75" customHeight="1">
+    <row r="78" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B78" s="9"/>
-      <c r="C78" s="33" t="s">
-        <v>93</v>
-      </c>
+      <c r="C78" s="18"/>
       <c r="D78" s="9"/>
-      <c r="F78" s="225" t="s">
-        <v>189</v>
-      </c>
-      <c r="G78" s="225"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
       <c r="H78" s="18"/>
       <c r="I78" s="18"/>
       <c r="J78" s="18"/>
@@ -7188,15 +7224,12 @@
       <c r="Y78" s="18"/>
       <c r="Z78" s="18"/>
     </row>
-    <row r="79" spans="2:26" ht="18" customHeight="1">
-      <c r="B79" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
+    <row r="79" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="9"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="9"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="18"/>
       <c r="H79" s="18"/>
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
@@ -7217,13 +7250,12 @@
       <c r="Y79" s="18"/>
       <c r="Z79" s="18"/>
     </row>
-    <row r="80" spans="2:26" ht="15.75" thickBot="1">
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
+    <row r="80" spans="2:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="217"/>
+      <c r="C80" s="217"/>
+      <c r="D80" s="217"/>
+      <c r="F80" s="218"/>
+      <c r="G80" s="218"/>
       <c r="H80" s="18"/>
       <c r="I80" s="18"/>
       <c r="J80" s="18"/>
@@ -7244,73 +7276,101 @@
       <c r="Y80" s="18"/>
       <c r="Z80" s="18"/>
     </row>
-    <row r="81" spans="2:26" ht="24" customHeight="1">
-      <c r="B81" s="214" t="s">
-        <v>191</v>
-      </c>
-      <c r="C81" s="215"/>
-      <c r="D81" s="215"/>
-      <c r="E81" s="215"/>
-      <c r="F81" s="215"/>
-      <c r="G81" s="216"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="9"/>
-      <c r="M81" s="9"/>
-      <c r="N81" s="9"/>
-      <c r="O81" s="9"/>
-      <c r="P81" s="9"/>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
-      <c r="V81" s="9"/>
-      <c r="W81" s="9"/>
-      <c r="X81" s="9"/>
-      <c r="Y81" s="9"/>
-      <c r="Z81" s="9"/>
-    </row>
-    <row r="82" spans="2:26" ht="13.5" customHeight="1">
-      <c r="B82" s="217" t="s">
-        <v>192</v>
-      </c>
-      <c r="C82" s="218"/>
-      <c r="D82" s="218"/>
-      <c r="E82" s="218"/>
-      <c r="F82" s="218"/>
-      <c r="G82" s="219"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="37"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
-      <c r="M82" s="9"/>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
-      <c r="P82" s="9"/>
-      <c r="Q82" s="9"/>
-      <c r="R82" s="9"/>
-      <c r="S82" s="9"/>
-      <c r="T82" s="9"/>
-      <c r="U82" s="9"/>
-      <c r="V82" s="9"/>
-      <c r="W82" s="9"/>
-      <c r="X82" s="9"/>
-      <c r="Y82" s="9"/>
-      <c r="Z82" s="9"/>
-    </row>
-    <row r="83" spans="2:26" s="10" customFormat="1" ht="156" customHeight="1" thickBot="1">
-      <c r="B83" s="121"/>
-      <c r="C83" s="121"/>
-      <c r="D83" s="121"/>
-      <c r="E83" s="121"/>
-      <c r="F83" s="121"/>
-      <c r="G83" s="122"/>
-    </row>
-    <row r="84" spans="2:26">
+    <row r="81" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="9"/>
+      <c r="C81" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D81" s="9"/>
+      <c r="F81" s="241" t="s">
+        <v>168</v>
+      </c>
+      <c r="G81" s="241"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="18"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+      <c r="P81" s="18"/>
+      <c r="Q81" s="18"/>
+      <c r="R81" s="18"/>
+      <c r="S81" s="18"/>
+      <c r="T81" s="18"/>
+      <c r="U81" s="18"/>
+      <c r="V81" s="18"/>
+      <c r="W81" s="18"/>
+      <c r="X81" s="18"/>
+      <c r="Y81" s="18"/>
+      <c r="Z81" s="18"/>
+    </row>
+    <row r="82" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="18"/>
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+      <c r="P82" s="18"/>
+      <c r="Q82" s="18"/>
+      <c r="R82" s="18"/>
+      <c r="S82" s="18"/>
+      <c r="T82" s="18"/>
+      <c r="U82" s="18"/>
+      <c r="V82" s="18"/>
+      <c r="W82" s="18"/>
+      <c r="X82" s="18"/>
+      <c r="Y82" s="18"/>
+      <c r="Z82" s="18"/>
+    </row>
+    <row r="83" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
+      <c r="L83" s="18"/>
+      <c r="M83" s="18"/>
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+      <c r="P83" s="18"/>
+      <c r="Q83" s="18"/>
+      <c r="R83" s="18"/>
+      <c r="S83" s="18"/>
+      <c r="T83" s="18"/>
+      <c r="U83" s="18"/>
+      <c r="V83" s="18"/>
+      <c r="W83" s="18"/>
+      <c r="X83" s="18"/>
+      <c r="Y83" s="18"/>
+      <c r="Z83" s="18"/>
+    </row>
+    <row r="84" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="228" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="229"/>
+      <c r="D84" s="229"/>
+      <c r="E84" s="229"/>
+      <c r="F84" s="229"/>
+      <c r="G84" s="230"/>
       <c r="H84" s="10"/>
       <c r="I84" s="9"/>
       <c r="J84" s="9"/>
@@ -7331,19 +7391,131 @@
       <c r="Y84" s="9"/>
       <c r="Z84" s="9"/>
     </row>
+    <row r="85" spans="2:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="231" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="232"/>
+      <c r="D85" s="232"/>
+      <c r="E85" s="232"/>
+      <c r="F85" s="232"/>
+      <c r="G85" s="233"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="37"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="9"/>
+      <c r="O85" s="9"/>
+      <c r="P85" s="9"/>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
+      <c r="V85" s="9"/>
+      <c r="W85" s="9"/>
+      <c r="X85" s="9"/>
+      <c r="Y85" s="9"/>
+      <c r="Z85" s="9"/>
+    </row>
+    <row r="86" spans="2:26" s="10" customFormat="1" ht="156" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="116"/>
+      <c r="C86" s="116"/>
+      <c r="D86" s="116"/>
+      <c r="E86" s="116"/>
+      <c r="F86" s="116"/>
+      <c r="G86" s="117"/>
+    </row>
+    <row r="87" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="H87" s="10"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="9"/>
+      <c r="K87" s="9"/>
+      <c r="L87" s="9"/>
+      <c r="M87" s="9"/>
+      <c r="N87" s="9"/>
+      <c r="O87" s="9"/>
+      <c r="P87" s="9"/>
+      <c r="Q87" s="9"/>
+      <c r="R87" s="9"/>
+      <c r="S87" s="9"/>
+      <c r="T87" s="9"/>
+      <c r="U87" s="9"/>
+      <c r="V87" s="9"/>
+      <c r="W87" s="9"/>
+      <c r="X87" s="9"/>
+      <c r="Y87" s="9"/>
+      <c r="Z87" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="B58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
+  <mergeCells count="80">
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="B60:C61"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="B84:G84"/>
+    <mergeCell ref="B85:G85"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
     <mergeCell ref="B52:C53"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="E52:E53"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B80:D80"/>
     <mergeCell ref="B54:C55"/>
     <mergeCell ref="D54:D55"/>
     <mergeCell ref="E54:E55"/>
@@ -7354,65 +7526,17 @@
     <mergeCell ref="E56:E57"/>
     <mergeCell ref="F56:F57"/>
     <mergeCell ref="G56:G57"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="B81:G81"/>
-    <mergeCell ref="B82:G82"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F23" r:id="rId1" xr:uid="{1A04884D-E1E4-4504-B262-077F3F1E0EF3}"/>
-    <hyperlink ref="F11" r:id="rId2" xr:uid="{03C4974F-814F-4626-829A-20AFC5ABD49C}"/>
-    <hyperlink ref="G11" r:id="rId3" xr:uid="{79037C3E-4F9C-4257-A8D5-8AEA1AF78E84}"/>
-    <hyperlink ref="F20" r:id="rId4" xr:uid="{3FF9481A-01FE-4DA6-9186-E94E212DBD41}"/>
+    <hyperlink ref="F20" r:id="rId1" xr:uid="{3FF9481A-01FE-4DA6-9186-E94E212DBD41}"/>
+    <hyperlink ref="G11" r:id="rId2" xr:uid="{79037C3E-4F9C-4257-A8D5-8AEA1AF78E84}"/>
+    <hyperlink ref="F11" r:id="rId3" xr:uid="{03C4974F-814F-4626-829A-20AFC5ABD49C}"/>
+    <hyperlink ref="F23" r:id="rId4" xr:uid="{1A04884D-E1E4-4504-B262-077F3F1E0EF3}"/>
   </hyperlinks>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="4294967294" r:id="rId5"/>
@@ -7438,64 +7562,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D237D29B-37DE-45D6-8EA7-98C4A952DFFE}">
   <dimension ref="D1:D12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="4:4">
+    <row r="1" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="4:4">
+    <row r="2" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="4:4">
+    <row r="3" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="4:4">
+    <row r="4" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="4:4">
+    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="4:4">
+    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="4:4">
+    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D7">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="4:4">
+    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="4:4">
+    <row r="9" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="4:4">
+    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="4:4">
+    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>12</v>
       </c>
@@ -7511,134 +7635,134 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="20" width="5.7109375" style="1" customWidth="1"/>
     <col min="21" max="24" width="8.42578125" style="1" customWidth="1"/>
     <col min="25" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="18.75">
-      <c r="A1" s="287" t="s">
-        <v>193</v>
-      </c>
-      <c r="B1" s="287"/>
-      <c r="C1" s="287"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="287"/>
-      <c r="F1" s="287"/>
-      <c r="G1" s="287"/>
-      <c r="H1" s="287"/>
-      <c r="I1" s="287"/>
-      <c r="J1" s="287"/>
-      <c r="K1" s="287"/>
-      <c r="L1" s="287"/>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287" t="s">
-        <v>194</v>
-      </c>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-    </row>
-    <row r="2" spans="1:24" ht="33" customHeight="1">
-      <c r="A2" s="287"/>
-      <c r="B2" s="287"/>
-      <c r="C2" s="287"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="287"/>
-      <c r="F2" s="287"/>
-      <c r="G2" s="287"/>
-      <c r="H2" s="287"/>
-      <c r="I2" s="287"/>
-      <c r="J2" s="287"/>
-      <c r="K2" s="287"/>
-      <c r="L2" s="287"/>
-      <c r="M2" s="287"/>
-      <c r="N2" s="287"/>
-      <c r="O2" s="287"/>
-      <c r="P2" s="287"/>
-      <c r="Q2" s="287"/>
-      <c r="R2" s="287"/>
-      <c r="S2" s="287"/>
-      <c r="T2" s="287"/>
-      <c r="U2" s="267" t="s">
-        <v>195</v>
-      </c>
-      <c r="V2" s="267"/>
-      <c r="W2" s="267"/>
-      <c r="X2" s="267"/>
-    </row>
-    <row r="3" spans="1:24" ht="33" customHeight="1" thickBot="1">
-      <c r="U3" s="294"/>
-      <c r="V3" s="294"/>
-      <c r="W3" s="294"/>
-      <c r="X3" s="294"/>
-    </row>
-    <row r="4" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="291" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="292"/>
-      <c r="C4" s="292"/>
-      <c r="D4" s="292"/>
-      <c r="E4" s="292"/>
-      <c r="F4" s="292"/>
-      <c r="G4" s="292"/>
-      <c r="H4" s="292"/>
-      <c r="I4" s="292"/>
-      <c r="J4" s="292"/>
-      <c r="K4" s="292"/>
-      <c r="L4" s="292"/>
-      <c r="M4" s="293"/>
-      <c r="N4" s="291" t="s">
-        <v>197</v>
-      </c>
-      <c r="O4" s="292"/>
-      <c r="P4" s="292"/>
-      <c r="Q4" s="292"/>
-      <c r="R4" s="292"/>
-      <c r="S4" s="292"/>
-      <c r="T4" s="292"/>
-      <c r="U4" s="292"/>
-      <c r="V4" s="292"/>
-      <c r="W4" s="292"/>
-      <c r="X4" s="293"/>
-    </row>
-    <row r="5" spans="1:24" ht="18" customHeight="1" thickBot="1">
-      <c r="A5" s="288"/>
-      <c r="B5" s="289"/>
-      <c r="C5" s="289"/>
-      <c r="D5" s="289"/>
-      <c r="E5" s="289"/>
-      <c r="F5" s="289"/>
-      <c r="G5" s="289"/>
-      <c r="H5" s="289"/>
-      <c r="I5" s="289"/>
-      <c r="J5" s="289"/>
-      <c r="K5" s="289"/>
-      <c r="L5" s="289"/>
-      <c r="M5" s="290"/>
-      <c r="N5" s="288"/>
-      <c r="O5" s="289"/>
-      <c r="P5" s="289"/>
-      <c r="Q5" s="289"/>
-      <c r="R5" s="289"/>
-      <c r="S5" s="289"/>
-      <c r="T5" s="289"/>
-      <c r="U5" s="289"/>
-      <c r="V5" s="289"/>
-      <c r="W5" s="289"/>
-      <c r="X5" s="290"/>
-    </row>
-    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="1" spans="1:24" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="246" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="246"/>
+      <c r="P1" s="246"/>
+      <c r="Q1" s="246"/>
+      <c r="R1" s="246"/>
+      <c r="S1" s="246"/>
+      <c r="T1" s="246"/>
+      <c r="U1" s="246" t="s">
+        <v>173</v>
+      </c>
+      <c r="V1" s="246"/>
+      <c r="W1" s="246"/>
+      <c r="X1" s="246"/>
+    </row>
+    <row r="2" spans="1:24" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="246"/>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="M2" s="246"/>
+      <c r="N2" s="246"/>
+      <c r="O2" s="246"/>
+      <c r="P2" s="246"/>
+      <c r="Q2" s="246"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="254" t="s">
+        <v>174</v>
+      </c>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+    </row>
+    <row r="3" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U3" s="255"/>
+      <c r="V3" s="255"/>
+      <c r="W3" s="255"/>
+      <c r="X3" s="255"/>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="251" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="252"/>
+      <c r="C4" s="252"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="M4" s="253"/>
+      <c r="N4" s="251" t="s">
+        <v>176</v>
+      </c>
+      <c r="O4" s="252"/>
+      <c r="P4" s="252"/>
+      <c r="Q4" s="252"/>
+      <c r="R4" s="252"/>
+      <c r="S4" s="252"/>
+      <c r="T4" s="252"/>
+      <c r="U4" s="252"/>
+      <c r="V4" s="252"/>
+      <c r="W4" s="252"/>
+      <c r="X4" s="253"/>
+    </row>
+    <row r="5" spans="1:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="248"/>
+      <c r="B5" s="249"/>
+      <c r="C5" s="249"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="M5" s="250"/>
+      <c r="N5" s="248"/>
+      <c r="O5" s="249"/>
+      <c r="P5" s="249"/>
+      <c r="Q5" s="249"/>
+      <c r="R5" s="249"/>
+      <c r="S5" s="249"/>
+      <c r="T5" s="249"/>
+      <c r="U5" s="249"/>
+      <c r="V5" s="249"/>
+      <c r="W5" s="249"/>
+      <c r="X5" s="250"/>
+    </row>
+    <row r="6" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -7664,69 +7788,69 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="265" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="265"/>
-      <c r="C7" s="265"/>
-      <c r="D7" s="265"/>
-      <c r="E7" s="265"/>
-      <c r="F7" s="265"/>
-      <c r="G7" s="265"/>
-      <c r="H7" s="265"/>
-      <c r="I7" s="265"/>
-      <c r="J7" s="265" t="s">
+    <row r="7" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="247" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="247"/>
+      <c r="C7" s="247"/>
+      <c r="D7" s="247"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="247"/>
+      <c r="G7" s="247"/>
+      <c r="H7" s="247"/>
+      <c r="I7" s="247"/>
+      <c r="J7" s="247" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="265"/>
-      <c r="L7" s="265"/>
-      <c r="M7" s="265"/>
-      <c r="N7" s="265"/>
-      <c r="O7" s="265"/>
-      <c r="P7" s="265" t="s">
+      <c r="K7" s="247"/>
+      <c r="L7" s="247"/>
+      <c r="M7" s="247"/>
+      <c r="N7" s="247"/>
+      <c r="O7" s="247"/>
+      <c r="P7" s="247" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="265"/>
-      <c r="R7" s="265"/>
-      <c r="S7" s="265"/>
-      <c r="T7" s="265"/>
-      <c r="U7" s="265"/>
-      <c r="V7" s="265"/>
-      <c r="W7" s="265"/>
-      <c r="X7" s="265"/>
-    </row>
-    <row r="8" spans="1:24" ht="18" customHeight="1">
-      <c r="A8" s="272"/>
-      <c r="B8" s="272"/>
-      <c r="C8" s="272"/>
-      <c r="D8" s="272"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="272"/>
-      <c r="G8" s="272"/>
-      <c r="H8" s="272"/>
-      <c r="I8" s="272"/>
-      <c r="J8" s="273" t="s">
-        <v>199</v>
-      </c>
-      <c r="K8" s="274"/>
-      <c r="L8" s="274"/>
-      <c r="M8" s="274"/>
-      <c r="N8" s="274"/>
-      <c r="O8" s="275"/>
-      <c r="P8" s="273" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q8" s="274"/>
-      <c r="R8" s="274"/>
-      <c r="S8" s="274"/>
-      <c r="T8" s="274"/>
-      <c r="U8" s="274"/>
-      <c r="V8" s="274"/>
-      <c r="W8" s="274"/>
-      <c r="X8" s="275"/>
-    </row>
-    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1">
+      <c r="Q7" s="247"/>
+      <c r="R7" s="247"/>
+      <c r="S7" s="247"/>
+      <c r="T7" s="247"/>
+      <c r="U7" s="247"/>
+      <c r="V7" s="247"/>
+      <c r="W7" s="247"/>
+      <c r="X7" s="247"/>
+    </row>
+    <row r="8" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="256"/>
+      <c r="B8" s="256"/>
+      <c r="C8" s="256"/>
+      <c r="D8" s="256"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="256"/>
+      <c r="H8" s="256"/>
+      <c r="I8" s="256"/>
+      <c r="J8" s="257" t="s">
+        <v>178</v>
+      </c>
+      <c r="K8" s="258"/>
+      <c r="L8" s="258"/>
+      <c r="M8" s="258"/>
+      <c r="N8" s="258"/>
+      <c r="O8" s="259"/>
+      <c r="P8" s="257" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q8" s="258"/>
+      <c r="R8" s="258"/>
+      <c r="S8" s="258"/>
+      <c r="T8" s="258"/>
+      <c r="U8" s="258"/>
+      <c r="V8" s="258"/>
+      <c r="W8" s="258"/>
+      <c r="X8" s="259"/>
+    </row>
+    <row r="9" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -7752,69 +7876,69 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:24" ht="18" customHeight="1">
-      <c r="A10" s="285" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="285"/>
-      <c r="C10" s="285"/>
-      <c r="D10" s="285"/>
-      <c r="E10" s="285"/>
-      <c r="F10" s="285"/>
-      <c r="G10" s="285"/>
-      <c r="H10" s="285"/>
-      <c r="I10" s="285"/>
-      <c r="J10" s="285"/>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
-      <c r="M10" s="285"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
-      <c r="R10" s="285"/>
-      <c r="S10" s="285"/>
-      <c r="T10" s="285"/>
-      <c r="U10" s="285"/>
-      <c r="V10" s="285"/>
-      <c r="W10" s="285"/>
-      <c r="X10" s="285"/>
-    </row>
-    <row r="11" spans="1:24" ht="18" customHeight="1">
-      <c r="A11" s="286" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="286"/>
-      <c r="C11" s="286"/>
-      <c r="D11" s="286"/>
-      <c r="E11" s="286"/>
-      <c r="F11" s="286"/>
-      <c r="G11" s="286" t="s">
-        <v>202</v>
-      </c>
-      <c r="H11" s="286"/>
-      <c r="I11" s="286"/>
-      <c r="J11" s="286"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286" t="s">
-        <v>203</v>
-      </c>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="286"/>
-      <c r="Q11" s="286"/>
-      <c r="R11" s="286"/>
-      <c r="S11" s="286" t="s">
-        <v>204</v>
-      </c>
-      <c r="T11" s="286"/>
-      <c r="U11" s="286"/>
-      <c r="V11" s="286"/>
-      <c r="W11" s="286"/>
-      <c r="X11" s="286"/>
-    </row>
-    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1">
+    <row r="10" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="260" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="260"/>
+      <c r="C10" s="260"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="260"/>
+      <c r="L10" s="260"/>
+      <c r="M10" s="260"/>
+      <c r="N10" s="260"/>
+      <c r="O10" s="260"/>
+      <c r="P10" s="260"/>
+      <c r="Q10" s="260"/>
+      <c r="R10" s="260"/>
+      <c r="S10" s="260"/>
+      <c r="T10" s="260"/>
+      <c r="U10" s="260"/>
+      <c r="V10" s="260"/>
+      <c r="W10" s="260"/>
+      <c r="X10" s="260"/>
+    </row>
+    <row r="11" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="261" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="261"/>
+      <c r="C11" s="261"/>
+      <c r="D11" s="261"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="261" t="s">
+        <v>181</v>
+      </c>
+      <c r="H11" s="261"/>
+      <c r="I11" s="261"/>
+      <c r="J11" s="261"/>
+      <c r="K11" s="261"/>
+      <c r="L11" s="261"/>
+      <c r="M11" s="261" t="s">
+        <v>182</v>
+      </c>
+      <c r="N11" s="261"/>
+      <c r="O11" s="261"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="261"/>
+      <c r="S11" s="261" t="s">
+        <v>183</v>
+      </c>
+      <c r="T11" s="261"/>
+      <c r="U11" s="261"/>
+      <c r="V11" s="261"/>
+      <c r="W11" s="261"/>
+      <c r="X11" s="261"/>
+    </row>
+    <row r="12" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -7840,69 +7964,69 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="265" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="265"/>
-      <c r="C13" s="265"/>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="265" t="s">
+    <row r="13" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="247" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="247"/>
+      <c r="C13" s="247"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="247"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="247"/>
+      <c r="J13" s="247" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
-      <c r="M13" s="265"/>
-      <c r="N13" s="265"/>
-      <c r="O13" s="265"/>
-      <c r="P13" s="265" t="s">
+      <c r="K13" s="247"/>
+      <c r="L13" s="247"/>
+      <c r="M13" s="247"/>
+      <c r="N13" s="247"/>
+      <c r="O13" s="247"/>
+      <c r="P13" s="247" t="s">
         <v>58</v>
       </c>
-      <c r="Q13" s="265"/>
-      <c r="R13" s="265"/>
-      <c r="S13" s="265"/>
-      <c r="T13" s="265"/>
-      <c r="U13" s="265"/>
-      <c r="V13" s="265"/>
-      <c r="W13" s="265"/>
-      <c r="X13" s="265"/>
-    </row>
-    <row r="14" spans="1:24" ht="18" customHeight="1">
-      <c r="A14" s="272"/>
-      <c r="B14" s="272"/>
-      <c r="C14" s="272"/>
-      <c r="D14" s="272"/>
-      <c r="E14" s="272"/>
-      <c r="F14" s="272"/>
-      <c r="G14" s="272"/>
-      <c r="H14" s="272"/>
-      <c r="I14" s="272"/>
-      <c r="J14" s="273" t="s">
-        <v>206</v>
-      </c>
-      <c r="K14" s="274"/>
-      <c r="L14" s="274"/>
-      <c r="M14" s="274"/>
-      <c r="N14" s="274"/>
-      <c r="O14" s="275"/>
-      <c r="P14" s="273" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q14" s="274"/>
-      <c r="R14" s="274"/>
-      <c r="S14" s="274"/>
-      <c r="T14" s="274"/>
-      <c r="U14" s="274"/>
-      <c r="V14" s="274"/>
-      <c r="W14" s="274"/>
-      <c r="X14" s="275"/>
-    </row>
-    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1">
+      <c r="Q13" s="247"/>
+      <c r="R13" s="247"/>
+      <c r="S13" s="247"/>
+      <c r="T13" s="247"/>
+      <c r="U13" s="247"/>
+      <c r="V13" s="247"/>
+      <c r="W13" s="247"/>
+      <c r="X13" s="247"/>
+    </row>
+    <row r="14" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="256"/>
+      <c r="B14" s="256"/>
+      <c r="C14" s="256"/>
+      <c r="D14" s="256"/>
+      <c r="E14" s="256"/>
+      <c r="F14" s="256"/>
+      <c r="G14" s="256"/>
+      <c r="H14" s="256"/>
+      <c r="I14" s="256"/>
+      <c r="J14" s="257" t="s">
+        <v>185</v>
+      </c>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
+      <c r="M14" s="258"/>
+      <c r="N14" s="258"/>
+      <c r="O14" s="259"/>
+      <c r="P14" s="257" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q14" s="258"/>
+      <c r="R14" s="258"/>
+      <c r="S14" s="258"/>
+      <c r="T14" s="258"/>
+      <c r="U14" s="258"/>
+      <c r="V14" s="258"/>
+      <c r="W14" s="258"/>
+      <c r="X14" s="259"/>
+    </row>
+    <row r="15" spans="1:24" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -7928,185 +8052,173 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
     </row>
-    <row r="16" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="276" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="276"/>
-      <c r="C16" s="276"/>
-      <c r="D16" s="276"/>
-      <c r="E16" s="276"/>
-      <c r="F16" s="276"/>
-      <c r="G16" s="276"/>
-      <c r="H16" s="276"/>
-      <c r="I16" s="276"/>
-      <c r="J16" s="277" t="s">
-        <v>209</v>
-      </c>
-      <c r="K16" s="277"/>
-      <c r="L16" s="277"/>
-      <c r="M16" s="277"/>
-      <c r="N16" s="276" t="s">
-        <v>210</v>
-      </c>
-      <c r="O16" s="276"/>
-      <c r="P16" s="276"/>
-      <c r="Q16" s="276"/>
-      <c r="R16" s="276"/>
-      <c r="S16" s="276"/>
-      <c r="T16" s="278" t="s">
-        <v>211</v>
-      </c>
-      <c r="U16" s="278"/>
-      <c r="V16" s="278"/>
-      <c r="W16" s="278"/>
-      <c r="X16" s="278"/>
-    </row>
-    <row r="17" spans="1:24" ht="18" customHeight="1">
-      <c r="A17" s="266" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="267"/>
-      <c r="C17" s="267"/>
-      <c r="D17" s="267"/>
-      <c r="E17" s="267"/>
-      <c r="F17" s="267"/>
-      <c r="G17" s="267"/>
-      <c r="H17" s="267"/>
-      <c r="I17" s="268"/>
-      <c r="J17" s="279" t="s">
-        <v>213</v>
-      </c>
-      <c r="K17" s="280"/>
-      <c r="L17" s="280"/>
-      <c r="M17" s="281"/>
-      <c r="N17" s="266" t="s">
-        <v>214</v>
-      </c>
-      <c r="O17" s="267"/>
-      <c r="P17" s="267"/>
-      <c r="Q17" s="267"/>
-      <c r="R17" s="267"/>
-      <c r="S17" s="268"/>
-      <c r="T17" s="266" t="s">
-        <v>215</v>
-      </c>
-      <c r="U17" s="267"/>
-      <c r="V17" s="267"/>
-      <c r="W17" s="267"/>
-      <c r="X17" s="268"/>
-    </row>
-    <row r="18" spans="1:24" ht="48.75" customHeight="1">
-      <c r="A18" s="269"/>
-      <c r="B18" s="270"/>
-      <c r="C18" s="270"/>
-      <c r="D18" s="270"/>
-      <c r="E18" s="270"/>
-      <c r="F18" s="270"/>
-      <c r="G18" s="270"/>
-      <c r="H18" s="270"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="282"/>
-      <c r="K18" s="283"/>
-      <c r="L18" s="283"/>
-      <c r="M18" s="284"/>
-      <c r="N18" s="269"/>
-      <c r="O18" s="270"/>
-      <c r="P18" s="270"/>
-      <c r="Q18" s="270"/>
-      <c r="R18" s="270"/>
-      <c r="S18" s="271"/>
-      <c r="T18" s="269"/>
-      <c r="U18" s="270"/>
-      <c r="V18" s="270"/>
-      <c r="W18" s="270"/>
-      <c r="X18" s="271"/>
-    </row>
-    <row r="19" spans="1:24" ht="39" customHeight="1"/>
-    <row r="20" spans="1:24" ht="39" customHeight="1"/>
-    <row r="21" spans="1:24">
-      <c r="A21" s="264" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="264"/>
-      <c r="C21" s="264"/>
-      <c r="D21" s="264"/>
-      <c r="E21" s="264"/>
-      <c r="F21" s="264"/>
-      <c r="G21" s="264"/>
-      <c r="H21" s="264"/>
+    <row r="16" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="267" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="267"/>
+      <c r="C16" s="267"/>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
+      <c r="F16" s="267"/>
+      <c r="G16" s="267"/>
+      <c r="H16" s="267"/>
+      <c r="I16" s="267"/>
+      <c r="J16" s="268" t="s">
+        <v>188</v>
+      </c>
+      <c r="K16" s="268"/>
+      <c r="L16" s="268"/>
+      <c r="M16" s="268"/>
+      <c r="N16" s="267" t="s">
+        <v>189</v>
+      </c>
+      <c r="O16" s="267"/>
+      <c r="P16" s="267"/>
+      <c r="Q16" s="267"/>
+      <c r="R16" s="267"/>
+      <c r="S16" s="267"/>
+      <c r="T16" s="269" t="s">
+        <v>190</v>
+      </c>
+      <c r="U16" s="269"/>
+      <c r="V16" s="269"/>
+      <c r="W16" s="269"/>
+      <c r="X16" s="269"/>
+    </row>
+    <row r="17" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="262" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="254"/>
+      <c r="C17" s="254"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="263"/>
+      <c r="J17" s="270" t="s">
+        <v>192</v>
+      </c>
+      <c r="K17" s="271"/>
+      <c r="L17" s="271"/>
+      <c r="M17" s="272"/>
+      <c r="N17" s="262" t="s">
+        <v>193</v>
+      </c>
+      <c r="O17" s="254"/>
+      <c r="P17" s="254"/>
+      <c r="Q17" s="254"/>
+      <c r="R17" s="254"/>
+      <c r="S17" s="263"/>
+      <c r="T17" s="262" t="s">
+        <v>194</v>
+      </c>
+      <c r="U17" s="254"/>
+      <c r="V17" s="254"/>
+      <c r="W17" s="254"/>
+      <c r="X17" s="263"/>
+    </row>
+    <row r="18" spans="1:24" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="264"/>
+      <c r="B18" s="265"/>
+      <c r="C18" s="265"/>
+      <c r="D18" s="265"/>
+      <c r="E18" s="265"/>
+      <c r="F18" s="265"/>
+      <c r="G18" s="265"/>
+      <c r="H18" s="265"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="273"/>
+      <c r="K18" s="274"/>
+      <c r="L18" s="274"/>
+      <c r="M18" s="275"/>
+      <c r="N18" s="264"/>
+      <c r="O18" s="265"/>
+      <c r="P18" s="265"/>
+      <c r="Q18" s="265"/>
+      <c r="R18" s="265"/>
+      <c r="S18" s="266"/>
+      <c r="T18" s="264"/>
+      <c r="U18" s="265"/>
+      <c r="V18" s="265"/>
+      <c r="W18" s="265"/>
+      <c r="X18" s="266"/>
+    </row>
+    <row r="19" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:24" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="279" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21" s="279"/>
+      <c r="C21" s="279"/>
+      <c r="D21" s="279"/>
+      <c r="E21" s="279"/>
+      <c r="F21" s="279"/>
+      <c r="G21" s="279"/>
+      <c r="H21" s="279"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="264" t="s">
-        <v>217</v>
-      </c>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
-      <c r="M21" s="264"/>
-      <c r="N21" s="264"/>
-      <c r="O21" s="264"/>
-      <c r="P21" s="264"/>
+      <c r="J21" s="279" t="s">
+        <v>196</v>
+      </c>
+      <c r="K21" s="279"/>
+      <c r="L21" s="279"/>
+      <c r="M21" s="279"/>
+      <c r="N21" s="279"/>
+      <c r="O21" s="279"/>
+      <c r="P21" s="279"/>
       <c r="Q21" s="6"/>
-      <c r="R21" s="264" t="s">
-        <v>218</v>
-      </c>
-      <c r="S21" s="264"/>
-      <c r="T21" s="264"/>
-      <c r="U21" s="264"/>
-      <c r="V21" s="264"/>
-      <c r="W21" s="264"/>
-      <c r="X21" s="264"/>
-    </row>
-    <row r="23" spans="1:24" ht="38.25" customHeight="1">
-      <c r="P23" s="261" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q23" s="261"/>
-      <c r="R23" s="261"/>
-      <c r="S23" s="261"/>
-      <c r="T23" s="261"/>
-      <c r="U23" s="262" t="s">
-        <v>220</v>
-      </c>
-      <c r="V23" s="262"/>
-      <c r="W23" s="262"/>
-      <c r="X23" s="262"/>
-    </row>
-    <row r="24" spans="1:24" ht="38.25" customHeight="1">
-      <c r="P24" s="261" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q24" s="261"/>
-      <c r="R24" s="261"/>
-      <c r="S24" s="261"/>
-      <c r="T24" s="261"/>
-      <c r="U24" s="263" t="s">
-        <v>222</v>
-      </c>
-      <c r="V24" s="263"/>
-      <c r="W24" s="263"/>
-      <c r="X24" s="263"/>
+      <c r="R21" s="279" t="s">
+        <v>197</v>
+      </c>
+      <c r="S21" s="279"/>
+      <c r="T21" s="279"/>
+      <c r="U21" s="279"/>
+      <c r="V21" s="279"/>
+      <c r="W21" s="279"/>
+      <c r="X21" s="279"/>
+    </row>
+    <row r="23" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="276" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q23" s="276"/>
+      <c r="R23" s="276"/>
+      <c r="S23" s="276"/>
+      <c r="T23" s="276"/>
+      <c r="U23" s="277" t="s">
+        <v>199</v>
+      </c>
+      <c r="V23" s="277"/>
+      <c r="W23" s="277"/>
+      <c r="X23" s="277"/>
+    </row>
+    <row r="24" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="276" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="276"/>
+      <c r="R24" s="276"/>
+      <c r="S24" s="276"/>
+      <c r="T24" s="276"/>
+      <c r="U24" s="278" t="s">
+        <v>201</v>
+      </c>
+      <c r="V24" s="278"/>
+      <c r="W24" s="278"/>
+      <c r="X24" s="278"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="N4:X4"/>
-    <mergeCell ref="N5:X5"/>
-    <mergeCell ref="U2:X3"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="A10:X10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="M11:R11"/>
-    <mergeCell ref="S11:X11"/>
+    <mergeCell ref="P23:T23"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="P24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="R21:X21"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="J13:O13"/>
     <mergeCell ref="P13:X13"/>
@@ -8121,13 +8233,25 @@
     <mergeCell ref="T16:X16"/>
     <mergeCell ref="A17:I18"/>
     <mergeCell ref="J17:M18"/>
-    <mergeCell ref="P23:T23"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="P24:T24"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="R21:X21"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="A10:X10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M11:R11"/>
+    <mergeCell ref="S11:X11"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:X4"/>
+    <mergeCell ref="N5:X5"/>
+    <mergeCell ref="U2:X3"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="95" orientation="landscape" horizontalDpi="4294967294" verticalDpi="200" r:id="rId1"/>
